--- a/research/traditional_assets/database/data/belgium/belgium_computer_services.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_computer_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09670781914840652</v>
+        <v>0.09649979960053551</v>
       </c>
       <c r="C2">
-        <v>826.8145822325589</v>
+        <v>818.9749994093717</v>
       </c>
       <c r="D2">
-        <v>547.7145822325589</v>
+        <v>548.5469994093717</v>
       </c>
       <c r="E2">
-        <v>-536.2</v>
+        <v>-527.528</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.672000000000001</v>
       </c>
       <c r="G2">
         <v>279.1</v>
@@ -1451,28 +1451,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4362016</v>
       </c>
       <c r="N2">
-        <v>80.40000000000001</v>
+        <v>79.9637984</v>
       </c>
       <c r="O2">
-        <v>20.1</v>
+        <v>19.9909496</v>
       </c>
       <c r="P2">
-        <v>60.3</v>
+        <v>59.9728488</v>
       </c>
       <c r="Q2">
-        <v>102.2</v>
+        <v>101.8728488</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09670781914840652</v>
+        <v>0.09709348444498536</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763955</v>
+        <v>0.999805484345156</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>184.3184435820501</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09649979960053551</v>
+        <v>0.09629178005266451</v>
       </c>
       <c r="C3">
-        <v>818.9749994093717</v>
+        <v>811.1379506544008</v>
       </c>
       <c r="D3">
-        <v>548.5469994093717</v>
+        <v>549.3819506544008</v>
       </c>
       <c r="E3">
-        <v>-527.528</v>
+        <v>-518.856</v>
       </c>
       <c r="F3">
-        <v>8.672000000000001</v>
+        <v>17.344</v>
       </c>
       <c r="G3">
         <v>279.1</v>
@@ -1533,28 +1533,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M3">
-        <v>0.4362016</v>
+        <v>0.8724032</v>
       </c>
       <c r="N3">
-        <v>79.9637984</v>
+        <v>79.52759680000001</v>
       </c>
       <c r="O3">
-        <v>19.9909496</v>
+        <v>19.8818992</v>
       </c>
       <c r="P3">
-        <v>59.9728488</v>
+        <v>59.64569760000001</v>
       </c>
       <c r="Q3">
-        <v>101.8728488</v>
+        <v>101.5456976</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09709348444498536</v>
+        <v>0.09748702046190255</v>
       </c>
       <c r="T3">
-        <v>0.999805484345156</v>
+        <v>1.007476233803075</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>184.3184435820501</v>
+        <v>92.15922179102508</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09629178005266451</v>
+        <v>0.09608376050479348</v>
       </c>
       <c r="C4">
-        <v>811.1379506544008</v>
+        <v>803.3034475567107</v>
       </c>
       <c r="D4">
-        <v>549.3819506544008</v>
+        <v>550.2194475567106</v>
       </c>
       <c r="E4">
-        <v>-518.856</v>
+        <v>-510.184</v>
       </c>
       <c r="F4">
-        <v>17.344</v>
+        <v>26.016</v>
       </c>
       <c r="G4">
         <v>279.1</v>
@@ -1615,28 +1615,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M4">
-        <v>0.8724032</v>
+        <v>1.3086048</v>
       </c>
       <c r="N4">
-        <v>79.52759680000001</v>
+        <v>79.09139520000001</v>
       </c>
       <c r="O4">
-        <v>19.8818992</v>
+        <v>19.7728488</v>
       </c>
       <c r="P4">
-        <v>59.64569760000001</v>
+        <v>59.3185464</v>
       </c>
       <c r="Q4">
-        <v>101.5456976</v>
+        <v>101.2185464</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09748702046190255</v>
+        <v>0.09788867062349843</v>
       </c>
       <c r="T4">
-        <v>1.007476233803075</v>
+        <v>1.015305143043631</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>92.15922179102508</v>
+        <v>61.43948119401671</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09608376050479348</v>
+        <v>0.09587574095692246</v>
       </c>
       <c r="C5">
-        <v>803.3034475567107</v>
+        <v>795.4715017761407</v>
       </c>
       <c r="D5">
-        <v>550.2194475567106</v>
+        <v>551.0595017761407</v>
       </c>
       <c r="E5">
-        <v>-510.184</v>
+        <v>-501.5120000000001</v>
       </c>
       <c r="F5">
-        <v>26.016</v>
+        <v>34.688</v>
       </c>
       <c r="G5">
         <v>279.1</v>
@@ -1697,28 +1697,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M5">
-        <v>1.3086048</v>
+        <v>1.7448064</v>
       </c>
       <c r="N5">
-        <v>79.09139520000001</v>
+        <v>78.6551936</v>
       </c>
       <c r="O5">
-        <v>19.7728488</v>
+        <v>19.6637984</v>
       </c>
       <c r="P5">
-        <v>59.3185464</v>
+        <v>58.9913952</v>
       </c>
       <c r="Q5">
-        <v>101.2185464</v>
+        <v>100.8913952</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09788867062349843</v>
+        <v>0.09829868849679424</v>
       </c>
       <c r="T5">
-        <v>1.015305143043631</v>
+        <v>1.023297154560033</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>61.43948119401671</v>
+        <v>46.07961089551253</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09587574095692246</v>
+        <v>0.09566772140905146</v>
       </c>
       <c r="C6">
-        <v>795.4715017761407</v>
+        <v>787.6421250438464</v>
       </c>
       <c r="D6">
-        <v>551.0595017761407</v>
+        <v>551.9021250438464</v>
       </c>
       <c r="E6">
-        <v>-501.5120000000001</v>
+        <v>-492.84</v>
       </c>
       <c r="F6">
-        <v>34.688</v>
+        <v>43.36000000000001</v>
       </c>
       <c r="G6">
         <v>279.1</v>
@@ -1779,28 +1779,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M6">
-        <v>1.7448064</v>
+        <v>2.181008</v>
       </c>
       <c r="N6">
-        <v>78.6551936</v>
+        <v>78.218992</v>
       </c>
       <c r="O6">
-        <v>19.6637984</v>
+        <v>19.554748</v>
       </c>
       <c r="P6">
-        <v>58.9913952</v>
+        <v>58.664244</v>
       </c>
       <c r="Q6">
-        <v>100.8913952</v>
+        <v>100.564244</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09829868849679424</v>
+        <v>0.09871733832531732</v>
       </c>
       <c r="T6">
-        <v>1.023297154560033</v>
+        <v>1.031457418950464</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>46.07961089551253</v>
+        <v>36.86368871641002</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09566772140905146</v>
+        <v>0.09545970186118043</v>
       </c>
       <c r="C7">
-        <v>787.6421250438464</v>
+        <v>779.8153291628455</v>
       </c>
       <c r="D7">
-        <v>551.9021250438464</v>
+        <v>552.7473291628455</v>
       </c>
       <c r="E7">
-        <v>-492.84</v>
+        <v>-484.1680000000001</v>
       </c>
       <c r="F7">
-        <v>43.36000000000001</v>
+        <v>52.032</v>
       </c>
       <c r="G7">
         <v>279.1</v>
@@ -1861,28 +1861,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M7">
-        <v>2.181008</v>
+        <v>2.6172096</v>
       </c>
       <c r="N7">
-        <v>78.218992</v>
+        <v>77.78279040000001</v>
       </c>
       <c r="O7">
-        <v>19.554748</v>
+        <v>19.4456976</v>
       </c>
       <c r="P7">
-        <v>58.664244</v>
+        <v>58.33709280000001</v>
       </c>
       <c r="Q7">
-        <v>100.564244</v>
+        <v>100.2370928</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09871733832531732</v>
+        <v>0.09914489559700046</v>
       </c>
       <c r="T7">
-        <v>1.031457418950464</v>
+        <v>1.039791305987499</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.86368871641002</v>
+        <v>30.71974059700836</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09545970186118043</v>
+        <v>0.09525168231330941</v>
       </c>
       <c r="C8">
-        <v>779.8153291628455</v>
+        <v>771.9911260085692</v>
       </c>
       <c r="D8">
-        <v>552.7473291628455</v>
+        <v>553.5951260085691</v>
       </c>
       <c r="E8">
-        <v>-484.1680000000001</v>
+        <v>-475.496</v>
       </c>
       <c r="F8">
-        <v>52.032</v>
+        <v>60.70399999999999</v>
       </c>
       <c r="G8">
         <v>279.1</v>
@@ -1943,28 +1943,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M8">
-        <v>2.6172096</v>
+        <v>3.053411199999999</v>
       </c>
       <c r="N8">
-        <v>77.78279040000001</v>
+        <v>77.34658880000001</v>
       </c>
       <c r="O8">
-        <v>19.4456976</v>
+        <v>19.3366472</v>
       </c>
       <c r="P8">
-        <v>58.33709280000001</v>
+        <v>58.0099416</v>
       </c>
       <c r="Q8">
-        <v>100.2370928</v>
+        <v>99.9099416</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09914489559700046</v>
+        <v>0.0995816476487198</v>
       </c>
       <c r="T8">
-        <v>1.039791305987499</v>
+        <v>1.048304416401676</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.71974059700836</v>
+        <v>26.33120622600717</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0952516823133094</v>
+        <v>0.09504366276543841</v>
       </c>
       <c r="C9">
-        <v>771.9911260085692</v>
+        <v>764.1695275294175</v>
       </c>
       <c r="D9">
-        <v>553.5951260085691</v>
+        <v>554.4455275294174</v>
       </c>
       <c r="E9">
-        <v>-475.496</v>
+        <v>-466.8240000000001</v>
       </c>
       <c r="F9">
-        <v>60.70400000000001</v>
+        <v>69.376</v>
       </c>
       <c r="G9">
         <v>279.1</v>
@@ -2025,28 +2025,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M9">
-        <v>3.0534112</v>
+        <v>3.4896128</v>
       </c>
       <c r="N9">
-        <v>77.34658880000001</v>
+        <v>76.9103872</v>
       </c>
       <c r="O9">
-        <v>19.3366472</v>
+        <v>19.2275968</v>
       </c>
       <c r="P9">
-        <v>58.0099416</v>
+        <v>57.6827904</v>
       </c>
       <c r="Q9">
-        <v>99.9099416</v>
+        <v>99.58279039999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0995816476487198</v>
+        <v>0.1000278943102591</v>
       </c>
       <c r="T9">
-        <v>1.048304416401676</v>
+        <v>1.057002594433552</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.33120622600716</v>
+        <v>23.03980544775627</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09504366276543841</v>
+        <v>0.09483564321756736</v>
       </c>
       <c r="C10">
-        <v>764.1695275294175</v>
+        <v>756.3505457473219</v>
       </c>
       <c r="D10">
-        <v>554.4455275294174</v>
+        <v>555.2985457473219</v>
       </c>
       <c r="E10">
-        <v>-466.8240000000001</v>
+        <v>-458.152</v>
       </c>
       <c r="F10">
-        <v>69.376</v>
+        <v>78.048</v>
       </c>
       <c r="G10">
         <v>279.1</v>
@@ -2107,28 +2107,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M10">
-        <v>3.4896128</v>
+        <v>3.9258144</v>
       </c>
       <c r="N10">
-        <v>76.9103872</v>
+        <v>76.47418560000001</v>
       </c>
       <c r="O10">
-        <v>19.2275968</v>
+        <v>19.1185464</v>
       </c>
       <c r="P10">
-        <v>57.6827904</v>
+        <v>57.35563920000001</v>
       </c>
       <c r="Q10">
-        <v>99.58279039999999</v>
+        <v>99.25563920000002</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1000278943102591</v>
+        <v>0.1004839485907334</v>
       </c>
       <c r="T10">
-        <v>1.057002594433552</v>
+        <v>1.065891941213381</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.03980544775627</v>
+        <v>20.47982706467224</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09483564321756736</v>
+        <v>0.09462762366969638</v>
       </c>
       <c r="C11">
-        <v>756.3505457473219</v>
+        <v>748.5341927583108</v>
       </c>
       <c r="D11">
-        <v>555.2985457473219</v>
+        <v>556.1541927583108</v>
       </c>
       <c r="E11">
-        <v>-458.152</v>
+        <v>-449.48</v>
       </c>
       <c r="F11">
-        <v>78.048</v>
+        <v>86.72</v>
       </c>
       <c r="G11">
         <v>279.1</v>
@@ -2189,28 +2189,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M11">
-        <v>3.9258144</v>
+        <v>4.362016</v>
       </c>
       <c r="N11">
-        <v>76.47418560000001</v>
+        <v>76.03798400000001</v>
       </c>
       <c r="O11">
-        <v>19.1185464</v>
+        <v>19.009496</v>
       </c>
       <c r="P11">
-        <v>57.35563920000001</v>
+        <v>57.02848800000001</v>
       </c>
       <c r="Q11">
-        <v>99.25563920000002</v>
+        <v>98.92848800000002</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1004839485907334</v>
+        <v>0.1009501374107737</v>
       </c>
       <c r="T11">
-        <v>1.065891941213381</v>
+        <v>1.074978829032762</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.47982706467224</v>
+        <v>18.43184435820502</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09462762366969638</v>
+        <v>0.09441960412182535</v>
       </c>
       <c r="C12">
-        <v>748.5341927583108</v>
+        <v>740.720480733082</v>
       </c>
       <c r="D12">
-        <v>556.1541927583108</v>
+        <v>557.012480733082</v>
       </c>
       <c r="E12">
-        <v>-449.48</v>
+        <v>-440.808</v>
       </c>
       <c r="F12">
-        <v>86.72000000000001</v>
+        <v>95.39200000000001</v>
       </c>
       <c r="G12">
         <v>279.1</v>
@@ -2271,28 +2271,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M12">
-        <v>4.362016000000001</v>
+        <v>4.7982176</v>
       </c>
       <c r="N12">
-        <v>76.03798400000001</v>
+        <v>75.6017824</v>
       </c>
       <c r="O12">
-        <v>19.009496</v>
+        <v>18.9004456</v>
       </c>
       <c r="P12">
-        <v>57.02848800000001</v>
+        <v>56.70133680000001</v>
       </c>
       <c r="Q12">
-        <v>98.92848800000002</v>
+        <v>98.60133680000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009501374107737</v>
+        <v>0.1014268023840734</v>
       </c>
       <c r="T12">
-        <v>1.074978829032762</v>
+        <v>1.084269916578421</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.43184435820501</v>
+        <v>16.75622214382274</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09441960412182535</v>
+        <v>0.09421158457395433</v>
       </c>
       <c r="C13">
-        <v>740.720480733082</v>
+        <v>732.9094219175792</v>
       </c>
       <c r="D13">
-        <v>557.012480733082</v>
+        <v>557.8734219175791</v>
       </c>
       <c r="E13">
-        <v>-440.808</v>
+        <v>-432.136</v>
       </c>
       <c r="F13">
-        <v>95.39200000000001</v>
+        <v>104.064</v>
       </c>
       <c r="G13">
         <v>279.1</v>
@@ -2353,28 +2353,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M13">
-        <v>4.7982176</v>
+        <v>5.2344192</v>
       </c>
       <c r="N13">
-        <v>75.6017824</v>
+        <v>75.1655808</v>
       </c>
       <c r="O13">
-        <v>18.9004456</v>
+        <v>18.7913952</v>
       </c>
       <c r="P13">
-        <v>56.70133680000001</v>
+        <v>56.3741856</v>
       </c>
       <c r="Q13">
-        <v>98.60133680000001</v>
+        <v>98.27418560000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1014268023840734</v>
+        <v>0.1019143006522208</v>
       </c>
       <c r="T13">
-        <v>1.084269916578421</v>
+        <v>1.093772165204663</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.75622214382274</v>
+        <v>15.35987029850418</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09421158457395433</v>
+        <v>0.09400356502608331</v>
       </c>
       <c r="C14">
-        <v>732.9094219175792</v>
+        <v>725.1010286335739</v>
       </c>
       <c r="D14">
-        <v>557.8734219175791</v>
+        <v>558.7370286335739</v>
       </c>
       <c r="E14">
-        <v>-432.136</v>
+        <v>-423.4640000000001</v>
       </c>
       <c r="F14">
-        <v>104.064</v>
+        <v>112.736</v>
       </c>
       <c r="G14">
         <v>279.1</v>
@@ -2435,28 +2435,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M14">
-        <v>5.2344192</v>
+        <v>5.6706208</v>
       </c>
       <c r="N14">
-        <v>75.1655808</v>
+        <v>74.72937920000001</v>
       </c>
       <c r="O14">
-        <v>18.7913952</v>
+        <v>18.6823448</v>
       </c>
       <c r="P14">
-        <v>56.3741856</v>
+        <v>56.04703440000001</v>
       </c>
       <c r="Q14">
-        <v>98.27418560000001</v>
+        <v>97.94703440000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1019143006522208</v>
+        <v>0.1024130057771073</v>
       </c>
       <c r="T14">
-        <v>1.093772165204663</v>
+        <v>1.10349285632806</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.35987029850418</v>
+        <v>14.17834181400386</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09400356502608331</v>
+        <v>0.0937955454782123</v>
       </c>
       <c r="C15">
-        <v>725.1010286335739</v>
+        <v>717.2953132792555</v>
       </c>
       <c r="D15">
-        <v>558.7370286335739</v>
+        <v>559.6033132792555</v>
       </c>
       <c r="E15">
-        <v>-423.4640000000001</v>
+        <v>-414.792</v>
       </c>
       <c r="F15">
-        <v>112.736</v>
+        <v>121.408</v>
       </c>
       <c r="G15">
         <v>279.1</v>
@@ -2517,28 +2517,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M15">
-        <v>5.6706208</v>
+        <v>6.1068224</v>
       </c>
       <c r="N15">
-        <v>74.72937920000001</v>
+        <v>74.29317760000001</v>
       </c>
       <c r="O15">
-        <v>18.6823448</v>
+        <v>18.5732944</v>
       </c>
       <c r="P15">
-        <v>56.04703440000001</v>
+        <v>55.71988320000001</v>
       </c>
       <c r="Q15">
-        <v>97.94703440000001</v>
+        <v>97.6198832</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1024130057771073</v>
+        <v>0.1029233086955957</v>
       </c>
       <c r="T15">
-        <v>1.10349285632806</v>
+        <v>1.113439610035723</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.17834181400386</v>
+        <v>13.16560311300358</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0937955454782123</v>
+        <v>0.09375627593034128</v>
       </c>
       <c r="C16">
-        <v>717.2953132792555</v>
+        <v>708.7871504065663</v>
       </c>
       <c r="D16">
-        <v>559.6033132792555</v>
+        <v>559.7671504065663</v>
       </c>
       <c r="E16">
-        <v>-414.792</v>
+        <v>-406.12</v>
       </c>
       <c r="F16">
-        <v>121.408</v>
+        <v>130.08</v>
       </c>
       <c r="G16">
         <v>279.1</v>
@@ -2599,45 +2599,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M16">
-        <v>6.1068224</v>
+        <v>6.738144</v>
       </c>
       <c r="N16">
-        <v>74.29317760000001</v>
+        <v>73.661856</v>
       </c>
       <c r="O16">
-        <v>18.5732944</v>
+        <v>18.415464</v>
       </c>
       <c r="P16">
-        <v>55.71988320000001</v>
+        <v>55.246392</v>
       </c>
       <c r="Q16">
-        <v>97.6198832</v>
+        <v>97.14639199999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1029233086955957</v>
+        <v>0.103445618741578</v>
       </c>
       <c r="T16">
-        <v>1.113439610035723</v>
+        <v>1.123620405007095</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.16560311300358</v>
+        <v>11.93206912764108</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09375627593034128</v>
+        <v>0.09355950638247026</v>
       </c>
       <c r="C17">
-        <v>708.7871504065663</v>
+        <v>700.937542688979</v>
       </c>
       <c r="D17">
-        <v>559.7671504065663</v>
+        <v>560.589542688979</v>
       </c>
       <c r="E17">
-        <v>-406.12</v>
+        <v>-397.448</v>
       </c>
       <c r="F17">
-        <v>130.08</v>
+        <v>138.752</v>
       </c>
       <c r="G17">
         <v>279.1</v>
@@ -2681,28 +2681,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M17">
-        <v>6.738144</v>
+        <v>7.187353600000001</v>
       </c>
       <c r="N17">
-        <v>73.661856</v>
+        <v>73.21264640000001</v>
       </c>
       <c r="O17">
-        <v>18.415464</v>
+        <v>18.3031616</v>
       </c>
       <c r="P17">
-        <v>55.246392</v>
+        <v>54.90948480000001</v>
       </c>
       <c r="Q17">
-        <v>97.14639199999999</v>
+        <v>96.80948480000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.103445618741578</v>
+        <v>0.103980364741036</v>
       </c>
       <c r="T17">
-        <v>1.123620405007095</v>
+        <v>1.134043599858738</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.93206912764108</v>
+        <v>11.18631480716352</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09355950638247026</v>
+        <v>0.09336273683459925</v>
       </c>
       <c r="C18">
-        <v>700.937542688979</v>
+        <v>693.0903549925346</v>
       </c>
       <c r="D18">
-        <v>560.589542688979</v>
+        <v>561.4143549925345</v>
       </c>
       <c r="E18">
-        <v>-397.448</v>
+        <v>-388.7760000000001</v>
       </c>
       <c r="F18">
-        <v>138.752</v>
+        <v>147.424</v>
       </c>
       <c r="G18">
         <v>279.1</v>
@@ -2763,28 +2763,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M18">
-        <v>7.187353600000001</v>
+        <v>7.6365632</v>
       </c>
       <c r="N18">
-        <v>73.21264640000001</v>
+        <v>72.76343680000001</v>
       </c>
       <c r="O18">
-        <v>18.3031616</v>
+        <v>18.1908592</v>
       </c>
       <c r="P18">
-        <v>54.90948480000001</v>
+        <v>54.5725776</v>
       </c>
       <c r="Q18">
-        <v>96.80948480000001</v>
+        <v>96.47257759999999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.103980364741036</v>
+        <v>0.1045279961862642</v>
       </c>
       <c r="T18">
-        <v>1.134043599858738</v>
+        <v>1.144717956032107</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.18631480716352</v>
+        <v>10.52829628909507</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09336273683459925</v>
+        <v>0.09316596728672823</v>
       </c>
       <c r="C19">
-        <v>693.0903549925346</v>
+        <v>685.2455980149232</v>
       </c>
       <c r="D19">
-        <v>561.4143549925345</v>
+        <v>562.2415980149232</v>
       </c>
       <c r="E19">
-        <v>-388.7760000000001</v>
+        <v>-380.104</v>
       </c>
       <c r="F19">
-        <v>147.424</v>
+        <v>156.096</v>
       </c>
       <c r="G19">
         <v>279.1</v>
@@ -2845,28 +2845,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M19">
-        <v>7.6365632</v>
+        <v>8.085772800000001</v>
       </c>
       <c r="N19">
-        <v>72.76343680000001</v>
+        <v>72.3142272</v>
       </c>
       <c r="O19">
-        <v>18.1908592</v>
+        <v>18.0785568</v>
       </c>
       <c r="P19">
-        <v>54.5725776</v>
+        <v>54.2356704</v>
       </c>
       <c r="Q19">
-        <v>96.47257759999999</v>
+        <v>96.13567040000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1045279961862642</v>
+        <v>0.10508898449601</v>
       </c>
       <c r="T19">
-        <v>1.144717956032107</v>
+        <v>1.155652662356046</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.52829628909507</v>
+        <v>9.943390939700903</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09316596728672824</v>
+        <v>0.09321144773885721</v>
       </c>
       <c r="C20">
-        <v>685.2455980149231</v>
+        <v>676.3821761365332</v>
       </c>
       <c r="D20">
-        <v>562.2415980149231</v>
+        <v>562.0501761365332</v>
       </c>
       <c r="E20">
-        <v>-380.104</v>
+        <v>-371.432</v>
       </c>
       <c r="F20">
-        <v>156.096</v>
+        <v>164.768</v>
       </c>
       <c r="G20">
         <v>279.1</v>
@@ -2927,45 +2927,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M20">
-        <v>8.085772800000001</v>
+        <v>8.815087999999999</v>
       </c>
       <c r="N20">
-        <v>72.3142272</v>
+        <v>71.584912</v>
       </c>
       <c r="O20">
-        <v>18.0785568</v>
+        <v>17.896228</v>
       </c>
       <c r="P20">
-        <v>54.2356704</v>
+        <v>53.688684</v>
       </c>
       <c r="Q20">
-        <v>96.13567040000001</v>
+        <v>95.588684</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.10508898449601</v>
+        <v>0.1056638243689595</v>
       </c>
       <c r="T20">
-        <v>1.155652662356046</v>
+        <v>1.166857361428724</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.943390939700903</v>
+        <v>9.120725737508236</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09321144773885721</v>
+        <v>0.09302742819098621</v>
       </c>
       <c r="C21">
-        <v>676.3821761365332</v>
+        <v>668.4854971395296</v>
       </c>
       <c r="D21">
-        <v>562.0501761365332</v>
+        <v>562.8254971395296</v>
       </c>
       <c r="E21">
-        <v>-371.432</v>
+        <v>-362.76</v>
       </c>
       <c r="F21">
-        <v>164.768</v>
+        <v>173.44</v>
       </c>
       <c r="G21">
         <v>279.1</v>
@@ -3009,28 +3009,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M21">
-        <v>8.815087999999999</v>
+        <v>9.279040000000002</v>
       </c>
       <c r="N21">
-        <v>71.584912</v>
+        <v>71.12096</v>
       </c>
       <c r="O21">
-        <v>17.896228</v>
+        <v>17.78024</v>
       </c>
       <c r="P21">
-        <v>53.688684</v>
+        <v>53.34072</v>
       </c>
       <c r="Q21">
-        <v>95.588684</v>
+        <v>95.24072</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1056638243689595</v>
+        <v>0.1062530352387328</v>
       </c>
       <c r="T21">
-        <v>1.166857361428724</v>
+        <v>1.17834217797822</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.120725737508236</v>
+        <v>8.664689450632821</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09302742819098621</v>
+        <v>0.09284340864311517</v>
       </c>
       <c r="C22">
-        <v>668.4854971395296</v>
+        <v>660.5909601328619</v>
       </c>
       <c r="D22">
-        <v>562.8254971395296</v>
+        <v>563.602960132862</v>
       </c>
       <c r="E22">
-        <v>-362.76</v>
+        <v>-354.088</v>
       </c>
       <c r="F22">
-        <v>173.44</v>
+        <v>182.112</v>
       </c>
       <c r="G22">
         <v>279.1</v>
@@ -3091,28 +3091,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M22">
-        <v>9.279040000000002</v>
+        <v>9.742992000000001</v>
       </c>
       <c r="N22">
-        <v>71.12096</v>
+        <v>70.657008</v>
       </c>
       <c r="O22">
-        <v>17.78024</v>
+        <v>17.664252</v>
       </c>
       <c r="P22">
-        <v>53.34072</v>
+        <v>52.992756</v>
       </c>
       <c r="Q22">
-        <v>95.24072</v>
+        <v>94.89275599999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1062530352387328</v>
+        <v>0.1068571628393863</v>
       </c>
       <c r="T22">
-        <v>1.17834217797822</v>
+        <v>1.190117749377069</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.664689450632821</v>
+        <v>8.25208519107888</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09284340864311517</v>
+        <v>0.09265938909524417</v>
       </c>
       <c r="C23">
-        <v>660.5909601328621</v>
+        <v>652.6985740053691</v>
       </c>
       <c r="D23">
-        <v>563.602960132862</v>
+        <v>564.3825740053691</v>
       </c>
       <c r="E23">
-        <v>-354.0880000000001</v>
+        <v>-345.4160000000001</v>
       </c>
       <c r="F23">
-        <v>182.112</v>
+        <v>190.784</v>
       </c>
       <c r="G23">
         <v>279.1</v>
@@ -3173,28 +3173,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M23">
-        <v>9.742991999999999</v>
+        <v>10.206944</v>
       </c>
       <c r="N23">
-        <v>70.657008</v>
+        <v>70.19305600000001</v>
       </c>
       <c r="O23">
-        <v>17.664252</v>
+        <v>17.548264</v>
       </c>
       <c r="P23">
-        <v>52.992756</v>
+        <v>52.64479200000001</v>
       </c>
       <c r="Q23">
-        <v>94.89275599999999</v>
+        <v>94.544792</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1068571628393863</v>
+        <v>0.1074767808913387</v>
       </c>
       <c r="T23">
-        <v>1.190117749377069</v>
+        <v>1.202195258504094</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.25208519107888</v>
+        <v>7.876990409666205</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09265938909524417</v>
+        <v>0.09261336954737315</v>
       </c>
       <c r="C24">
-        <v>652.6985740053691</v>
+        <v>644.2218768357939</v>
       </c>
       <c r="D24">
-        <v>564.3825740053691</v>
+        <v>564.5778768357939</v>
       </c>
       <c r="E24">
-        <v>-345.4160000000001</v>
+        <v>-336.744</v>
       </c>
       <c r="F24">
-        <v>190.784</v>
+        <v>199.456</v>
       </c>
       <c r="G24">
         <v>279.1</v>
@@ -3255,45 +3255,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M24">
-        <v>10.206944</v>
+        <v>10.8304608</v>
       </c>
       <c r="N24">
-        <v>70.19305600000001</v>
+        <v>69.56953920000001</v>
       </c>
       <c r="O24">
-        <v>17.548264</v>
+        <v>17.3923848</v>
       </c>
       <c r="P24">
-        <v>52.64479200000001</v>
+        <v>52.17715440000001</v>
       </c>
       <c r="Q24">
-        <v>94.544792</v>
+        <v>94.07715440000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1074767808913387</v>
+        <v>0.1081124929186664</v>
       </c>
       <c r="T24">
-        <v>1.202195258504094</v>
+        <v>1.214586469166887</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.876990409666205</v>
+        <v>7.42350685577478</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09261336954737315</v>
+        <v>0.09243534999950215</v>
       </c>
       <c r="C25">
-        <v>644.2218768357939</v>
+        <v>636.3066502949288</v>
       </c>
       <c r="D25">
-        <v>564.5778768357939</v>
+        <v>565.3346502949288</v>
       </c>
       <c r="E25">
-        <v>-336.744</v>
+        <v>-328.072</v>
       </c>
       <c r="F25">
-        <v>199.456</v>
+        <v>208.128</v>
       </c>
       <c r="G25">
         <v>279.1</v>
@@ -3337,28 +3337,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M25">
-        <v>10.8304608</v>
+        <v>11.3013504</v>
       </c>
       <c r="N25">
-        <v>69.56953920000001</v>
+        <v>69.0986496</v>
       </c>
       <c r="O25">
-        <v>17.3923848</v>
+        <v>17.2746624</v>
       </c>
       <c r="P25">
-        <v>52.17715440000001</v>
+        <v>51.8239872</v>
       </c>
       <c r="Q25">
-        <v>94.07715440000001</v>
+        <v>93.72398720000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1081124929186664</v>
+        <v>0.1087649342098712</v>
       </c>
       <c r="T25">
-        <v>1.214586469166887</v>
+        <v>1.227303764320805</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.42350685577478</v>
+        <v>7.114194070117497</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09243534999950215</v>
+        <v>0.09225733045163112</v>
       </c>
       <c r="C26">
-        <v>636.3066502949288</v>
+        <v>628.3934552710291</v>
       </c>
       <c r="D26">
-        <v>565.3346502949288</v>
+        <v>566.0934552710291</v>
       </c>
       <c r="E26">
-        <v>-328.072</v>
+        <v>-319.4</v>
       </c>
       <c r="F26">
-        <v>208.128</v>
+        <v>216.8</v>
       </c>
       <c r="G26">
         <v>279.1</v>
@@ -3419,28 +3419,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M26">
-        <v>11.3013504</v>
+        <v>11.77224</v>
       </c>
       <c r="N26">
-        <v>69.0986496</v>
+        <v>68.62776000000001</v>
       </c>
       <c r="O26">
-        <v>17.2746624</v>
+        <v>17.15694</v>
       </c>
       <c r="P26">
-        <v>51.8239872</v>
+        <v>51.47082</v>
       </c>
       <c r="Q26">
-        <v>93.72398720000001</v>
+        <v>93.37082000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1087649342098712</v>
+        <v>0.1094347739355082</v>
       </c>
       <c r="T26">
-        <v>1.227303764320805</v>
+        <v>1.240360187345494</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.114194070117497</v>
+        <v>6.829626307312798</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09225733045163112</v>
+        <v>0.09207931090376009</v>
       </c>
       <c r="C27">
-        <v>628.3934552710291</v>
+        <v>620.4822999553335</v>
       </c>
       <c r="D27">
-        <v>566.0934552710291</v>
+        <v>566.8542999553334</v>
       </c>
       <c r="E27">
-        <v>-319.4</v>
+        <v>-310.7280000000001</v>
       </c>
       <c r="F27">
-        <v>216.8</v>
+        <v>225.472</v>
       </c>
       <c r="G27">
         <v>279.1</v>
@@ -3501,28 +3501,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M27">
-        <v>11.77224</v>
+        <v>12.2431296</v>
       </c>
       <c r="N27">
-        <v>68.62776000000001</v>
+        <v>68.1568704</v>
       </c>
       <c r="O27">
-        <v>17.15694</v>
+        <v>17.0392176</v>
       </c>
       <c r="P27">
-        <v>51.47082</v>
+        <v>51.1176528</v>
       </c>
       <c r="Q27">
-        <v>93.37082000000001</v>
+        <v>93.01765280000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1094347739355082</v>
+        <v>0.1101227174375136</v>
       </c>
       <c r="T27">
-        <v>1.240360187345494</v>
+        <v>1.253769486668148</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.829626307312798</v>
+        <v>6.56694837241615</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09207931090376009</v>
+        <v>0.09190129135588909</v>
       </c>
       <c r="C28">
-        <v>620.4822999553335</v>
+        <v>612.5731925831768</v>
       </c>
       <c r="D28">
-        <v>566.8542999553334</v>
+        <v>567.6171925831768</v>
       </c>
       <c r="E28">
-        <v>-310.7280000000001</v>
+        <v>-302.056</v>
       </c>
       <c r="F28">
-        <v>225.472</v>
+        <v>234.144</v>
       </c>
       <c r="G28">
         <v>279.1</v>
@@ -3583,28 +3583,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M28">
-        <v>12.2431296</v>
+        <v>12.7140192</v>
       </c>
       <c r="N28">
-        <v>68.1568704</v>
+        <v>67.68598080000001</v>
       </c>
       <c r="O28">
-        <v>17.0392176</v>
+        <v>16.9214952</v>
       </c>
       <c r="P28">
-        <v>51.1176528</v>
+        <v>50.76448560000001</v>
       </c>
       <c r="Q28">
-        <v>93.01765280000001</v>
+        <v>92.66448560000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1101227174375136</v>
+        <v>0.1108295087066974</v>
       </c>
       <c r="T28">
-        <v>1.253769486668148</v>
+        <v>1.267546164054437</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.56694837241615</v>
+        <v>6.323728062326664</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09190129135588909</v>
+        <v>0.09193327180801807</v>
       </c>
       <c r="C29">
-        <v>612.5731925831768</v>
+        <v>603.7639909024514</v>
       </c>
       <c r="D29">
-        <v>567.6171925831768</v>
+        <v>567.4799909024514</v>
       </c>
       <c r="E29">
-        <v>-302.056</v>
+        <v>-293.384</v>
       </c>
       <c r="F29">
-        <v>234.144</v>
+        <v>242.816</v>
       </c>
       <c r="G29">
         <v>279.1</v>
@@ -3665,45 +3665,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M29">
-        <v>12.7140192</v>
+        <v>13.4277248</v>
       </c>
       <c r="N29">
-        <v>67.68598080000001</v>
+        <v>66.9722752</v>
       </c>
       <c r="O29">
-        <v>16.9214952</v>
+        <v>16.7430688</v>
       </c>
       <c r="P29">
-        <v>50.76448560000001</v>
+        <v>50.2292064</v>
       </c>
       <c r="Q29">
-        <v>92.66448560000001</v>
+        <v>92.12920639999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1108295087066974</v>
+        <v>0.1115559330666918</v>
       </c>
       <c r="T29">
-        <v>1.267546164054437</v>
+        <v>1.281705526923677</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.323728062326664</v>
+        <v>5.987611542351537</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09193327180801807</v>
+        <v>0.09176275226014705</v>
       </c>
       <c r="C30">
-        <v>603.7639909024514</v>
+        <v>595.8243163173665</v>
       </c>
       <c r="D30">
-        <v>567.4799909024514</v>
+        <v>568.2123163173666</v>
       </c>
       <c r="E30">
-        <v>-293.384</v>
+        <v>-284.712</v>
       </c>
       <c r="F30">
-        <v>242.816</v>
+        <v>251.4880000000001</v>
       </c>
       <c r="G30">
         <v>279.1</v>
@@ -3747,28 +3747,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M30">
-        <v>13.4277248</v>
+        <v>13.9072864</v>
       </c>
       <c r="N30">
-        <v>66.9722752</v>
+        <v>66.4927136</v>
       </c>
       <c r="O30">
-        <v>16.7430688</v>
+        <v>16.6231784</v>
       </c>
       <c r="P30">
-        <v>50.2292064</v>
+        <v>49.8695352</v>
       </c>
       <c r="Q30">
-        <v>92.12920639999999</v>
+        <v>91.76953520000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1115559330666918</v>
+        <v>0.1123028200847142</v>
       </c>
       <c r="T30">
-        <v>1.281705526923677</v>
+        <v>1.296263745085009</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.987611542351537</v>
+        <v>5.781142178822174</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09176275226014705</v>
+        <v>0.09159223271227603</v>
       </c>
       <c r="C31">
-        <v>595.8243163173665</v>
+        <v>587.8865342871027</v>
       </c>
       <c r="D31">
-        <v>568.2123163173666</v>
+        <v>568.9465342871027</v>
       </c>
       <c r="E31">
-        <v>-284.712</v>
+        <v>-276.04</v>
       </c>
       <c r="F31">
-        <v>251.488</v>
+        <v>260.16</v>
       </c>
       <c r="G31">
         <v>279.1</v>
@@ -3829,28 +3829,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M31">
-        <v>13.9072864</v>
+        <v>14.386848</v>
       </c>
       <c r="N31">
-        <v>66.4927136</v>
+        <v>66.01315200000001</v>
       </c>
       <c r="O31">
-        <v>16.6231784</v>
+        <v>16.503288</v>
       </c>
       <c r="P31">
-        <v>49.8695352</v>
+        <v>49.50986400000001</v>
       </c>
       <c r="Q31">
-        <v>91.76953520000001</v>
+        <v>91.409864</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1123028200847142</v>
+        <v>0.1130710467318229</v>
       </c>
       <c r="T31">
-        <v>1.296263745085009</v>
+        <v>1.311237912336665</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.781142178822175</v>
+        <v>5.588437439528102</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09159223271227603</v>
+        <v>0.09142171316440501</v>
       </c>
       <c r="C32">
-        <v>587.8865342871027</v>
+        <v>579.9506521575706</v>
       </c>
       <c r="D32">
-        <v>568.9465342871027</v>
+        <v>569.6826521575706</v>
       </c>
       <c r="E32">
-        <v>-276.04</v>
+        <v>-267.3680000000001</v>
       </c>
       <c r="F32">
-        <v>260.16</v>
+        <v>268.832</v>
       </c>
       <c r="G32">
         <v>279.1</v>
@@ -3911,28 +3911,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M32">
-        <v>14.386848</v>
+        <v>14.8664096</v>
       </c>
       <c r="N32">
-        <v>66.01315200000001</v>
+        <v>65.53359040000001</v>
       </c>
       <c r="O32">
-        <v>16.503288</v>
+        <v>16.3833976</v>
       </c>
       <c r="P32">
-        <v>49.50986400000001</v>
+        <v>49.15019280000001</v>
       </c>
       <c r="Q32">
-        <v>91.409864</v>
+        <v>91.0501928</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1130710467318229</v>
+        <v>0.1138615408179783</v>
       </c>
       <c r="T32">
-        <v>1.311237912336665</v>
+        <v>1.326646113421702</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.588437439528102</v>
+        <v>5.408165264059455</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09142171316440501</v>
+        <v>0.091251193616534</v>
       </c>
       <c r="C33">
-        <v>579.9506521575706</v>
+        <v>572.0166773127468</v>
       </c>
       <c r="D33">
-        <v>569.6826521575706</v>
+        <v>570.4206773127468</v>
       </c>
       <c r="E33">
-        <v>-267.3680000000001</v>
+        <v>-258.696</v>
       </c>
       <c r="F33">
-        <v>268.832</v>
+        <v>277.504</v>
       </c>
       <c r="G33">
         <v>279.1</v>
@@ -3993,28 +3993,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M33">
-        <v>14.8664096</v>
+        <v>15.3459712</v>
       </c>
       <c r="N33">
-        <v>65.53359040000001</v>
+        <v>65.0540288</v>
       </c>
       <c r="O33">
-        <v>16.3833976</v>
+        <v>16.2635072</v>
       </c>
       <c r="P33">
-        <v>49.15019280000001</v>
+        <v>48.7905216</v>
       </c>
       <c r="Q33">
-        <v>91.0501928</v>
+        <v>90.6905216</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1138615408179783</v>
+        <v>0.1146752847301971</v>
       </c>
       <c r="T33">
-        <v>1.326646113421702</v>
+        <v>1.342507496891594</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.408165264059455</v>
+        <v>5.239160099557595</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.091251193616534</v>
+        <v>0.09108067406866298</v>
       </c>
       <c r="C34">
-        <v>572.0166773127468</v>
+        <v>564.084617174922</v>
       </c>
       <c r="D34">
-        <v>570.4206773127468</v>
+        <v>571.160617174922</v>
       </c>
       <c r="E34">
-        <v>-258.696</v>
+        <v>-250.024</v>
       </c>
       <c r="F34">
-        <v>277.504</v>
+        <v>286.176</v>
       </c>
       <c r="G34">
         <v>279.1</v>
@@ -4075,28 +4075,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M34">
-        <v>15.3459712</v>
+        <v>15.8255328</v>
       </c>
       <c r="N34">
-        <v>65.0540288</v>
+        <v>64.5744672</v>
       </c>
       <c r="O34">
-        <v>16.2635072</v>
+        <v>16.1436168</v>
       </c>
       <c r="P34">
-        <v>48.7905216</v>
+        <v>48.4308504</v>
       </c>
       <c r="Q34">
-        <v>90.6905216</v>
+        <v>90.3308504</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1146752847301971</v>
+        <v>0.1155133195054671</v>
       </c>
       <c r="T34">
-        <v>1.342507496891594</v>
+        <v>1.358842354494915</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.239160099557595</v>
+        <v>5.080397672298274</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09108067406866298</v>
+        <v>0.09091015452079197</v>
       </c>
       <c r="C35">
-        <v>564.084617174922</v>
+        <v>556.154479204949</v>
       </c>
       <c r="D35">
-        <v>571.160617174922</v>
+        <v>571.9024792049489</v>
       </c>
       <c r="E35">
-        <v>-250.024</v>
+        <v>-241.352</v>
       </c>
       <c r="F35">
-        <v>286.176</v>
+        <v>294.848</v>
       </c>
       <c r="G35">
         <v>279.1</v>
@@ -4157,28 +4157,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M35">
-        <v>15.8255328</v>
+        <v>16.3050944</v>
       </c>
       <c r="N35">
-        <v>64.5744672</v>
+        <v>64.0949056</v>
       </c>
       <c r="O35">
-        <v>16.1436168</v>
+        <v>16.0237264</v>
       </c>
       <c r="P35">
-        <v>48.4308504</v>
+        <v>48.0711792</v>
       </c>
       <c r="Q35">
-        <v>90.3308504</v>
+        <v>89.97117919999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1155133195054671</v>
+        <v>0.1163767492739272</v>
       </c>
       <c r="T35">
-        <v>1.358842354494915</v>
+        <v>1.375672207783185</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.080397672298274</v>
+        <v>4.930974211348325</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09091015452079197</v>
+        <v>0.09073963497292095</v>
       </c>
       <c r="C36">
-        <v>556.154479204949</v>
+        <v>548.2262709024933</v>
       </c>
       <c r="D36">
-        <v>571.9024792049489</v>
+        <v>572.6462709024934</v>
       </c>
       <c r="E36">
-        <v>-241.352</v>
+        <v>-232.68</v>
       </c>
       <c r="F36">
-        <v>294.848</v>
+        <v>303.52</v>
       </c>
       <c r="G36">
         <v>279.1</v>
@@ -4239,28 +4239,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M36">
-        <v>16.3050944</v>
+        <v>16.784656</v>
       </c>
       <c r="N36">
-        <v>64.0949056</v>
+        <v>63.61534400000001</v>
       </c>
       <c r="O36">
-        <v>16.0237264</v>
+        <v>15.903836</v>
       </c>
       <c r="P36">
-        <v>48.0711792</v>
+        <v>47.71150800000001</v>
       </c>
       <c r="Q36">
-        <v>89.97117919999999</v>
+        <v>89.61150800000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1163767492739272</v>
+        <v>0.1172667461121861</v>
       </c>
       <c r="T36">
-        <v>1.375672207783185</v>
+        <v>1.393019902711094</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.930974211348325</v>
+        <v>4.790089233881231</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09073963497292095</v>
+        <v>0.09056911542504992</v>
       </c>
       <c r="C37">
-        <v>548.2262709024933</v>
+        <v>540.2999998062869</v>
       </c>
       <c r="D37">
-        <v>572.6462709024934</v>
+        <v>573.391999806287</v>
       </c>
       <c r="E37">
-        <v>-232.68</v>
+        <v>-224.008</v>
       </c>
       <c r="F37">
-        <v>303.52</v>
+        <v>312.1920000000001</v>
       </c>
       <c r="G37">
         <v>279.1</v>
@@ -4321,28 +4321,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M37">
-        <v>16.784656</v>
+        <v>17.26421760000001</v>
       </c>
       <c r="N37">
-        <v>63.61534400000001</v>
+        <v>63.1357824</v>
       </c>
       <c r="O37">
-        <v>15.903836</v>
+        <v>15.7839456</v>
       </c>
       <c r="P37">
-        <v>47.71150800000001</v>
+        <v>47.3518368</v>
       </c>
       <c r="Q37">
-        <v>89.61150800000001</v>
+        <v>89.25183680000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1172667461121861</v>
+        <v>0.1181845553516405</v>
       </c>
       <c r="T37">
-        <v>1.393019902711094</v>
+        <v>1.4109097131055</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.790089233881231</v>
+        <v>4.657031199606751</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09056911542504993</v>
+        <v>0.09039859587717891</v>
       </c>
       <c r="C38">
-        <v>540.2999998062869</v>
+        <v>532.3756734943817</v>
       </c>
       <c r="D38">
-        <v>573.3919998062869</v>
+        <v>574.1396734943817</v>
       </c>
       <c r="E38">
-        <v>-224.008</v>
+        <v>-215.336</v>
       </c>
       <c r="F38">
-        <v>312.192</v>
+        <v>320.864</v>
       </c>
       <c r="G38">
         <v>279.1</v>
@@ -4403,28 +4403,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M38">
-        <v>17.2642176</v>
+        <v>17.7437792</v>
       </c>
       <c r="N38">
-        <v>63.1357824</v>
+        <v>62.6562208</v>
       </c>
       <c r="O38">
-        <v>15.7839456</v>
+        <v>15.6640552</v>
       </c>
       <c r="P38">
-        <v>47.3518368</v>
+        <v>46.9921656</v>
       </c>
       <c r="Q38">
-        <v>89.25183680000001</v>
+        <v>88.8921656</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1181845553516405</v>
+        <v>0.1191315013923475</v>
       </c>
       <c r="T38">
-        <v>1.4109097131055</v>
+        <v>1.429367453988617</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.657031199606752</v>
+        <v>4.531165491509272</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09039859587717891</v>
+        <v>0.09094057632930791</v>
       </c>
       <c r="C39">
-        <v>532.3756734943817</v>
+        <v>521.3339849343349</v>
       </c>
       <c r="D39">
-        <v>574.1396734943817</v>
+        <v>571.7699849343348</v>
       </c>
       <c r="E39">
-        <v>-215.336</v>
+        <v>-206.664</v>
       </c>
       <c r="F39">
-        <v>320.864</v>
+        <v>329.536</v>
       </c>
       <c r="G39">
         <v>279.1</v>
@@ -4485,45 +4485,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M39">
-        <v>17.7437792</v>
+        <v>19.0471808</v>
       </c>
       <c r="N39">
-        <v>62.6562208</v>
+        <v>61.3528192</v>
       </c>
       <c r="O39">
-        <v>15.6640552</v>
+        <v>15.3382048</v>
       </c>
       <c r="P39">
-        <v>46.9921656</v>
+        <v>46.0146144</v>
       </c>
       <c r="Q39">
-        <v>88.8921656</v>
+        <v>87.9146144</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1191315013923475</v>
+        <v>0.1201089940795289</v>
       </c>
       <c r="T39">
-        <v>1.429367453988617</v>
+        <v>1.448420605867964</v>
       </c>
       <c r="U39">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.531165491509272</v>
+        <v>4.221097119002513</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09094057632930791</v>
+        <v>0.0907888067814369</v>
       </c>
       <c r="C40">
-        <v>521.3339849343349</v>
+        <v>513.3235892407176</v>
       </c>
       <c r="D40">
-        <v>571.7699849343348</v>
+        <v>572.4315892407176</v>
       </c>
       <c r="E40">
-        <v>-206.664</v>
+        <v>-197.992</v>
       </c>
       <c r="F40">
-        <v>329.536</v>
+        <v>338.208</v>
       </c>
       <c r="G40">
         <v>279.1</v>
@@ -4567,28 +4567,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M40">
-        <v>19.0471808</v>
+        <v>19.5484224</v>
       </c>
       <c r="N40">
-        <v>61.3528192</v>
+        <v>60.8515776</v>
       </c>
       <c r="O40">
-        <v>15.3382048</v>
+        <v>15.2128944</v>
       </c>
       <c r="P40">
-        <v>46.0146144</v>
+        <v>45.6386832</v>
       </c>
       <c r="Q40">
-        <v>87.9146144</v>
+        <v>87.53868320000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1201089940795289</v>
+        <v>0.1211185357072736</v>
       </c>
       <c r="T40">
-        <v>1.448420605867964</v>
+        <v>1.468098451251552</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.221097119002513</v>
+        <v>4.11286385954091</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0907888067814369</v>
+        <v>0.09063703723356586</v>
       </c>
       <c r="C41">
-        <v>513.3235892407176</v>
+        <v>505.3147264269289</v>
       </c>
       <c r="D41">
-        <v>572.4315892407176</v>
+        <v>573.0947264269289</v>
       </c>
       <c r="E41">
-        <v>-197.992</v>
+        <v>-189.32</v>
       </c>
       <c r="F41">
-        <v>338.208</v>
+        <v>346.8800000000001</v>
       </c>
       <c r="G41">
         <v>279.1</v>
@@ -4649,28 +4649,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M41">
-        <v>19.5484224</v>
+        <v>20.049664</v>
       </c>
       <c r="N41">
-        <v>60.8515776</v>
+        <v>60.350336</v>
       </c>
       <c r="O41">
-        <v>15.2128944</v>
+        <v>15.087584</v>
       </c>
       <c r="P41">
-        <v>45.6386832</v>
+        <v>45.262752</v>
       </c>
       <c r="Q41">
-        <v>87.53868320000001</v>
+        <v>87.162752</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1211185357072736</v>
+        <v>0.1221617287226098</v>
       </c>
       <c r="T41">
-        <v>1.468098451251552</v>
+        <v>1.488432224814593</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.11286385954091</v>
+        <v>4.010042263052387</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09063703723356586</v>
+        <v>0.09156151768569486</v>
       </c>
       <c r="C42">
-        <v>505.3147264269289</v>
+        <v>492.6269878484542</v>
       </c>
       <c r="D42">
-        <v>573.0947264269289</v>
+        <v>569.0789878484542</v>
       </c>
       <c r="E42">
-        <v>-189.32</v>
+        <v>-180.648</v>
       </c>
       <c r="F42">
-        <v>346.8800000000001</v>
+        <v>355.552</v>
       </c>
       <c r="G42">
         <v>279.1</v>
@@ -4731,45 +4731,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M42">
-        <v>20.049664</v>
+        <v>21.7953376</v>
       </c>
       <c r="N42">
-        <v>60.350336</v>
+        <v>58.60466240000001</v>
       </c>
       <c r="O42">
-        <v>15.087584</v>
+        <v>14.6511656</v>
       </c>
       <c r="P42">
-        <v>45.262752</v>
+        <v>43.95349680000001</v>
       </c>
       <c r="Q42">
-        <v>87.162752</v>
+        <v>85.85349680000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1221617287226098</v>
+        <v>0.1232402842130421</v>
       </c>
       <c r="T42">
-        <v>1.488432224814593</v>
+        <v>1.509455278837398</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.010042263052387</v>
+        <v>3.68886233723675</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09156151768569486</v>
+        <v>0.09143599813782385</v>
       </c>
       <c r="C43">
-        <v>492.6269878484542</v>
+        <v>484.4969120909462</v>
       </c>
       <c r="D43">
-        <v>569.0789878484542</v>
+        <v>569.6209120909463</v>
       </c>
       <c r="E43">
-        <v>-180.648</v>
+        <v>-171.976</v>
       </c>
       <c r="F43">
-        <v>355.552</v>
+        <v>364.224</v>
       </c>
       <c r="G43">
         <v>279.1</v>
@@ -4813,28 +4813,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M43">
-        <v>21.7953376</v>
+        <v>22.3269312</v>
       </c>
       <c r="N43">
-        <v>58.60466240000001</v>
+        <v>58.0730688</v>
       </c>
       <c r="O43">
-        <v>14.6511656</v>
+        <v>14.5182672</v>
       </c>
       <c r="P43">
-        <v>43.95349680000001</v>
+        <v>43.5548016</v>
       </c>
       <c r="Q43">
-        <v>85.85349680000002</v>
+        <v>85.4548016</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1232402842130421</v>
+        <v>0.1243560312721101</v>
       </c>
       <c r="T43">
-        <v>1.509455278837398</v>
+        <v>1.531203265757541</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.68886233723675</v>
+        <v>3.601032281588255</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09143599813782385</v>
+        <v>0.09131047858995282</v>
       </c>
       <c r="C44">
-        <v>484.4969120909463</v>
+        <v>476.367869447736</v>
       </c>
       <c r="D44">
-        <v>569.6209120909463</v>
+        <v>570.163869447736</v>
       </c>
       <c r="E44">
-        <v>-171.9760000000001</v>
+        <v>-163.304</v>
       </c>
       <c r="F44">
-        <v>364.224</v>
+        <v>372.896</v>
       </c>
       <c r="G44">
         <v>279.1</v>
@@ -4895,28 +4895,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M44">
-        <v>22.3269312</v>
+        <v>22.8585248</v>
       </c>
       <c r="N44">
-        <v>58.0730688</v>
+        <v>57.54147520000001</v>
       </c>
       <c r="O44">
-        <v>14.5182672</v>
+        <v>14.3853688</v>
       </c>
       <c r="P44">
-        <v>43.5548016</v>
+        <v>43.15610640000001</v>
       </c>
       <c r="Q44">
-        <v>85.4548016</v>
+        <v>85.0561064</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1243560312721101</v>
+        <v>0.1255109273507944</v>
       </c>
       <c r="T44">
-        <v>1.531203265757541</v>
+        <v>1.55371433993804</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.601032281588255</v>
+        <v>3.517287344807133</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09131047858995282</v>
+        <v>0.09210895904208183</v>
       </c>
       <c r="C45">
-        <v>476.367869447736</v>
+        <v>464.2594437094223</v>
       </c>
       <c r="D45">
-        <v>570.163869447736</v>
+        <v>566.7274437094223</v>
       </c>
       <c r="E45">
-        <v>-163.304</v>
+        <v>-154.632</v>
       </c>
       <c r="F45">
-        <v>372.896</v>
+        <v>381.568</v>
       </c>
       <c r="G45">
         <v>279.1</v>
@@ -4977,45 +4977,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M45">
-        <v>22.8585248</v>
+        <v>24.4585088</v>
       </c>
       <c r="N45">
-        <v>57.54147520000001</v>
+        <v>55.9414912</v>
       </c>
       <c r="O45">
-        <v>14.3853688</v>
+        <v>13.9853728</v>
       </c>
       <c r="P45">
-        <v>43.15610640000001</v>
+        <v>41.9561184</v>
       </c>
       <c r="Q45">
-        <v>85.0561064</v>
+        <v>83.8561184</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1255109273507944</v>
+        <v>0.1267070697180032</v>
       </c>
       <c r="T45">
-        <v>1.55371433993804</v>
+        <v>1.577029381053557</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.517287344807133</v>
+        <v>3.287199585937144</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09210895904208183</v>
+        <v>0.09200443949421079</v>
       </c>
       <c r="C46">
-        <v>464.2594437094223</v>
+        <v>456.0349071035017</v>
       </c>
       <c r="D46">
-        <v>566.7274437094223</v>
+        <v>567.1749071035017</v>
       </c>
       <c r="E46">
-        <v>-154.632</v>
+        <v>-145.96</v>
       </c>
       <c r="F46">
-        <v>381.568</v>
+        <v>390.24</v>
       </c>
       <c r="G46">
         <v>279.1</v>
@@ -5059,28 +5059,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M46">
-        <v>24.4585088</v>
+        <v>25.014384</v>
       </c>
       <c r="N46">
-        <v>55.9414912</v>
+        <v>55.385616</v>
       </c>
       <c r="O46">
-        <v>13.9853728</v>
+        <v>13.846404</v>
       </c>
       <c r="P46">
-        <v>41.9561184</v>
+        <v>41.539212</v>
       </c>
       <c r="Q46">
-        <v>83.8561184</v>
+        <v>83.439212</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1267070697180032</v>
+        <v>0.1279467081712923</v>
       </c>
       <c r="T46">
-        <v>1.577029381053557</v>
+        <v>1.601192241846002</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.287199585937144</v>
+        <v>3.214150706249652</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09200443949421079</v>
+        <v>0.09189991994633979</v>
       </c>
       <c r="C47">
-        <v>456.0349071035017</v>
+        <v>447.8110776512717</v>
       </c>
       <c r="D47">
-        <v>567.1749071035017</v>
+        <v>567.6230776512717</v>
       </c>
       <c r="E47">
-        <v>-145.96</v>
+        <v>-137.288</v>
       </c>
       <c r="F47">
-        <v>390.24</v>
+        <v>398.912</v>
       </c>
       <c r="G47">
         <v>279.1</v>
@@ -5141,28 +5141,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M47">
-        <v>25.014384</v>
+        <v>25.5702592</v>
       </c>
       <c r="N47">
-        <v>55.385616</v>
+        <v>54.8297408</v>
       </c>
       <c r="O47">
-        <v>13.846404</v>
+        <v>13.7074352</v>
       </c>
       <c r="P47">
-        <v>41.539212</v>
+        <v>41.1223056</v>
       </c>
       <c r="Q47">
-        <v>83.439212</v>
+        <v>83.02230560000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1279467081712923</v>
+        <v>0.1292322591598885</v>
       </c>
       <c r="T47">
-        <v>1.601192241846002</v>
+        <v>1.626250023408537</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.214150706249652</v>
+        <v>3.144277864809442</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09189991994633979</v>
+        <v>0.09179540039846876</v>
       </c>
       <c r="C48">
-        <v>447.8110776512717</v>
+        <v>439.5879570303956</v>
       </c>
       <c r="D48">
-        <v>567.6230776512717</v>
+        <v>568.0719570303957</v>
       </c>
       <c r="E48">
-        <v>-137.288</v>
+        <v>-128.616</v>
       </c>
       <c r="F48">
-        <v>398.912</v>
+        <v>407.5840000000001</v>
       </c>
       <c r="G48">
         <v>279.1</v>
@@ -5223,28 +5223,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M48">
-        <v>25.5702592</v>
+        <v>26.12613440000001</v>
       </c>
       <c r="N48">
-        <v>54.8297408</v>
+        <v>54.2738656</v>
       </c>
       <c r="O48">
-        <v>13.7074352</v>
+        <v>13.5684664</v>
       </c>
       <c r="P48">
-        <v>41.1223056</v>
+        <v>40.7053992</v>
       </c>
       <c r="Q48">
-        <v>83.02230560000001</v>
+        <v>82.60539919999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1292322591598885</v>
+        <v>0.1305663215065448</v>
       </c>
       <c r="T48">
-        <v>1.626250023408537</v>
+        <v>1.652253381633809</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.144277864809442</v>
+        <v>3.077378335770943</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09179540039846876</v>
+        <v>0.09169088085059776</v>
       </c>
       <c r="C49">
-        <v>439.5879570303956</v>
+        <v>431.3655469238466</v>
       </c>
       <c r="D49">
-        <v>568.0719570303957</v>
+        <v>568.5215469238466</v>
       </c>
       <c r="E49">
-        <v>-128.616</v>
+        <v>-119.944</v>
       </c>
       <c r="F49">
-        <v>407.5840000000001</v>
+        <v>416.256</v>
       </c>
       <c r="G49">
         <v>279.1</v>
@@ -5305,28 +5305,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M49">
-        <v>26.12613440000001</v>
+        <v>26.6820096</v>
       </c>
       <c r="N49">
-        <v>54.2738656</v>
+        <v>53.71799040000001</v>
       </c>
       <c r="O49">
-        <v>13.5684664</v>
+        <v>13.4294976</v>
       </c>
       <c r="P49">
-        <v>40.7053992</v>
+        <v>40.2884928</v>
       </c>
       <c r="Q49">
-        <v>82.60539919999999</v>
+        <v>82.18849280000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1305663215065448</v>
+        <v>0.1319516939434572</v>
       </c>
       <c r="T49">
-        <v>1.652253381633809</v>
+        <v>1.679256869021592</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.077378335770943</v>
+        <v>3.013266287109049</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09169088085059775</v>
+        <v>0.09445286130272672</v>
       </c>
       <c r="C50">
-        <v>431.3655469238466</v>
+        <v>411.0470838490706</v>
       </c>
       <c r="D50">
-        <v>568.5215469238466</v>
+        <v>556.8750838490706</v>
       </c>
       <c r="E50">
-        <v>-119.944</v>
+        <v>-111.272</v>
       </c>
       <c r="F50">
-        <v>416.256</v>
+        <v>424.928</v>
       </c>
       <c r="G50">
         <v>279.1</v>
@@ -5387,45 +5387,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M50">
-        <v>26.6820096</v>
+        <v>30.5523232</v>
       </c>
       <c r="N50">
-        <v>53.71799040000001</v>
+        <v>49.8476768</v>
       </c>
       <c r="O50">
-        <v>13.4294976</v>
+        <v>12.4619192</v>
       </c>
       <c r="P50">
-        <v>40.2884928</v>
+        <v>37.38575760000001</v>
       </c>
       <c r="Q50">
-        <v>82.18849280000001</v>
+        <v>79.28575760000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1319516939434572</v>
+        <v>0.1333913947112289</v>
       </c>
       <c r="T50">
-        <v>1.679256869021592</v>
+        <v>1.707319316699092</v>
       </c>
       <c r="U50">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.013266287109049</v>
+        <v>2.631551109016809</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09445286130272672</v>
+        <v>0.09440684175485571</v>
       </c>
       <c r="C51">
-        <v>411.0470838490706</v>
+        <v>402.5652244752976</v>
       </c>
       <c r="D51">
-        <v>556.8750838490706</v>
+        <v>557.0652244752976</v>
       </c>
       <c r="E51">
-        <v>-111.272</v>
+        <v>-102.6</v>
       </c>
       <c r="F51">
-        <v>424.928</v>
+        <v>433.6</v>
       </c>
       <c r="G51">
         <v>279.1</v>
@@ -5469,28 +5469,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M51">
-        <v>30.5523232</v>
+        <v>31.17584</v>
       </c>
       <c r="N51">
-        <v>49.8476768</v>
+        <v>49.22416</v>
       </c>
       <c r="O51">
-        <v>12.4619192</v>
+        <v>12.30604</v>
       </c>
       <c r="P51">
-        <v>37.38575760000001</v>
+        <v>36.91812</v>
       </c>
       <c r="Q51">
-        <v>79.28575760000001</v>
+        <v>78.81811999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1333913947112289</v>
+        <v>0.1348886835097114</v>
       </c>
       <c r="T51">
-        <v>1.707319316699092</v>
+        <v>1.736504262283692</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.631551109016809</v>
+        <v>2.578920086836473</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09440684175485571</v>
+        <v>0.0943608222069847</v>
       </c>
       <c r="C52">
-        <v>402.5652244752976</v>
+        <v>394.0834949899225</v>
       </c>
       <c r="D52">
-        <v>557.0652244752976</v>
+        <v>557.2554949899226</v>
       </c>
       <c r="E52">
-        <v>-102.6</v>
+        <v>-93.928</v>
       </c>
       <c r="F52">
-        <v>433.6</v>
+        <v>442.272</v>
       </c>
       <c r="G52">
         <v>279.1</v>
@@ -5551,28 +5551,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M52">
-        <v>31.17584</v>
+        <v>31.79935680000001</v>
       </c>
       <c r="N52">
-        <v>49.22416</v>
+        <v>48.6006432</v>
       </c>
       <c r="O52">
-        <v>12.30604</v>
+        <v>12.1501608</v>
       </c>
       <c r="P52">
-        <v>36.91812</v>
+        <v>36.4504824</v>
       </c>
       <c r="Q52">
-        <v>78.81811999999999</v>
+        <v>78.3504824</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1348886835097114</v>
+        <v>0.1364470861367035</v>
       </c>
       <c r="T52">
-        <v>1.736504262283692</v>
+        <v>1.766880430137051</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.578920086836473</v>
+        <v>2.528353026310268</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0943608222069847</v>
+        <v>0.09583580265911368</v>
       </c>
       <c r="C53">
-        <v>394.0834949899225</v>
+        <v>379.377079915076</v>
       </c>
       <c r="D53">
-        <v>557.2554949899226</v>
+        <v>551.221079915076</v>
       </c>
       <c r="E53">
-        <v>-93.928</v>
+        <v>-85.25600000000003</v>
       </c>
       <c r="F53">
-        <v>442.272</v>
+        <v>450.944</v>
       </c>
       <c r="G53">
         <v>279.1</v>
@@ -5633,45 +5633,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M53">
-        <v>31.79935680000001</v>
+        <v>34.18155520000001</v>
       </c>
       <c r="N53">
-        <v>48.6006432</v>
+        <v>46.2184448</v>
       </c>
       <c r="O53">
-        <v>12.1501608</v>
+        <v>11.5546112</v>
       </c>
       <c r="P53">
-        <v>36.4504824</v>
+        <v>34.6638336</v>
       </c>
       <c r="Q53">
-        <v>78.3504824</v>
+        <v>76.56383360000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1364470861367035</v>
+        <v>0.1380704222064868</v>
       </c>
       <c r="T53">
-        <v>1.766880430137051</v>
+        <v>1.798522271650967</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.528353026310268</v>
+        <v>2.352145756083093</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09583580265911368</v>
+        <v>0.09581903311124267</v>
       </c>
       <c r="C54">
-        <v>379.377079915076</v>
+        <v>370.7729526264328</v>
       </c>
       <c r="D54">
-        <v>551.221079915076</v>
+        <v>551.2889526264328</v>
       </c>
       <c r="E54">
-        <v>-85.25600000000003</v>
+        <v>-76.584</v>
       </c>
       <c r="F54">
-        <v>450.944</v>
+        <v>459.616</v>
       </c>
       <c r="G54">
         <v>279.1</v>
@@ -5715,28 +5715,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M54">
-        <v>34.18155520000001</v>
+        <v>34.8388928</v>
       </c>
       <c r="N54">
-        <v>46.2184448</v>
+        <v>45.5611072</v>
       </c>
       <c r="O54">
-        <v>11.5546112</v>
+        <v>11.3902768</v>
       </c>
       <c r="P54">
-        <v>34.6638336</v>
+        <v>34.1708304</v>
       </c>
       <c r="Q54">
-        <v>76.56383360000001</v>
+        <v>76.07083040000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1380704222064868</v>
+        <v>0.1397628364068993</v>
       </c>
       <c r="T54">
-        <v>1.798522271650967</v>
+        <v>1.8315105745059</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.352145756083093</v>
+        <v>2.307765647477752</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09581903311124267</v>
+        <v>0.09580226356337165</v>
       </c>
       <c r="C55">
-        <v>370.7729526264328</v>
+        <v>362.1688420543936</v>
       </c>
       <c r="D55">
-        <v>551.2889526264328</v>
+        <v>551.3568420543936</v>
       </c>
       <c r="E55">
-        <v>-76.584</v>
+        <v>-67.91199999999998</v>
       </c>
       <c r="F55">
-        <v>459.616</v>
+        <v>468.2880000000001</v>
       </c>
       <c r="G55">
         <v>279.1</v>
@@ -5797,28 +5797,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M55">
-        <v>34.8388928</v>
+        <v>35.49623040000001</v>
       </c>
       <c r="N55">
-        <v>45.5611072</v>
+        <v>44.9037696</v>
       </c>
       <c r="O55">
-        <v>11.3902768</v>
+        <v>11.2259424</v>
       </c>
       <c r="P55">
-        <v>34.1708304</v>
+        <v>33.6778272</v>
       </c>
       <c r="Q55">
-        <v>76.07083040000001</v>
+        <v>75.5778272</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1397628364068993</v>
+        <v>0.1415288338334166</v>
       </c>
       <c r="T55">
-        <v>1.8315105745059</v>
+        <v>1.865933151398005</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.307765647477752</v>
+        <v>2.265029246598534</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09580226356337165</v>
+        <v>0.09578549401550064</v>
       </c>
       <c r="C56">
-        <v>362.1688420543936</v>
+        <v>353.5647482051348</v>
       </c>
       <c r="D56">
-        <v>551.3568420543936</v>
+        <v>551.4247482051348</v>
       </c>
       <c r="E56">
-        <v>-67.91199999999998</v>
+        <v>-59.24000000000001</v>
       </c>
       <c r="F56">
-        <v>468.2880000000001</v>
+        <v>476.96</v>
       </c>
       <c r="G56">
         <v>279.1</v>
@@ -5879,28 +5879,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M56">
-        <v>35.49623040000001</v>
+        <v>36.15356800000001</v>
       </c>
       <c r="N56">
-        <v>44.9037696</v>
+        <v>44.246432</v>
       </c>
       <c r="O56">
-        <v>11.2259424</v>
+        <v>11.061608</v>
       </c>
       <c r="P56">
-        <v>33.6778272</v>
+        <v>33.184824</v>
       </c>
       <c r="Q56">
-        <v>75.5778272</v>
+        <v>75.084824</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1415288338334166</v>
+        <v>0.1433733200344459</v>
       </c>
       <c r="T56">
-        <v>1.865933151398005</v>
+        <v>1.901885620596425</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.265029246598534</v>
+        <v>2.223846896660379</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09578549401550064</v>
+        <v>0.09576872446762962</v>
       </c>
       <c r="C57">
-        <v>353.5647482051348</v>
+        <v>344.9606710848363</v>
       </c>
       <c r="D57">
-        <v>551.4247482051348</v>
+        <v>551.4926710848364</v>
       </c>
       <c r="E57">
-        <v>-59.24000000000001</v>
+        <v>-50.56799999999998</v>
       </c>
       <c r="F57">
-        <v>476.96</v>
+        <v>485.6320000000001</v>
       </c>
       <c r="G57">
         <v>279.1</v>
@@ -5961,28 +5961,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M57">
-        <v>36.15356800000001</v>
+        <v>36.81090560000001</v>
       </c>
       <c r="N57">
-        <v>44.246432</v>
+        <v>43.5890944</v>
       </c>
       <c r="O57">
-        <v>11.061608</v>
+        <v>10.8972736</v>
       </c>
       <c r="P57">
-        <v>33.184824</v>
+        <v>32.6918208</v>
       </c>
       <c r="Q57">
-        <v>75.084824</v>
+        <v>74.59182079999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1433733200344459</v>
+        <v>0.14530164651734</v>
       </c>
       <c r="T57">
-        <v>1.901885620596425</v>
+        <v>1.939472292940227</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.223846896660379</v>
+        <v>2.184135344934301</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09576872446762962</v>
+        <v>0.09575195491975859</v>
       </c>
       <c r="C58">
-        <v>344.9606710848363</v>
+        <v>336.3566106996806</v>
       </c>
       <c r="D58">
-        <v>551.4926710848364</v>
+        <v>551.5606106996806</v>
       </c>
       <c r="E58">
-        <v>-50.56799999999998</v>
+        <v>-41.89599999999996</v>
       </c>
       <c r="F58">
-        <v>485.6320000000001</v>
+        <v>494.3040000000001</v>
       </c>
       <c r="G58">
         <v>279.1</v>
@@ -6043,28 +6043,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M58">
-        <v>36.81090560000001</v>
+        <v>37.46824320000001</v>
       </c>
       <c r="N58">
-        <v>43.5890944</v>
+        <v>42.9317568</v>
       </c>
       <c r="O58">
-        <v>10.8972736</v>
+        <v>10.7329392</v>
       </c>
       <c r="P58">
-        <v>32.6918208</v>
+        <v>32.1988176</v>
       </c>
       <c r="Q58">
-        <v>74.59182079999999</v>
+        <v>74.09881759999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.14530164651734</v>
+        <v>0.1473196626040898</v>
       </c>
       <c r="T58">
-        <v>1.939472292940227</v>
+        <v>1.978807182602347</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.184135344934301</v>
+        <v>2.145817180988085</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09575195491975859</v>
+        <v>0.0957351853718876</v>
       </c>
       <c r="C59">
-        <v>336.3566106996806</v>
+        <v>327.752567055853</v>
       </c>
       <c r="D59">
-        <v>551.5606106996806</v>
+        <v>551.6285670558531</v>
       </c>
       <c r="E59">
-        <v>-41.89599999999996</v>
+        <v>-33.22399999999993</v>
       </c>
       <c r="F59">
-        <v>494.3040000000001</v>
+        <v>502.9760000000001</v>
       </c>
       <c r="G59">
         <v>279.1</v>
@@ -6125,28 +6125,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M59">
-        <v>37.46824320000001</v>
+        <v>38.12558080000001</v>
       </c>
       <c r="N59">
-        <v>42.9317568</v>
+        <v>42.2744192</v>
       </c>
       <c r="O59">
-        <v>10.7329392</v>
+        <v>10.5686048</v>
       </c>
       <c r="P59">
-        <v>32.1988176</v>
+        <v>31.7058144</v>
       </c>
       <c r="Q59">
-        <v>74.09881759999999</v>
+        <v>73.6058144</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1473196626040898</v>
+        <v>0.1494337746949705</v>
       </c>
       <c r="T59">
-        <v>1.978807182602347</v>
+        <v>2.020015162248377</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.145817180988085</v>
+        <v>2.108820333040015</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09573518537188759</v>
+        <v>0.09571841582401658</v>
       </c>
       <c r="C60">
-        <v>327.7525670558532</v>
+        <v>319.1485401595429</v>
       </c>
       <c r="D60">
-        <v>551.6285670558532</v>
+        <v>551.6965401595429</v>
       </c>
       <c r="E60">
-        <v>-33.22400000000005</v>
+        <v>-24.55200000000002</v>
       </c>
       <c r="F60">
-        <v>502.976</v>
+        <v>511.648</v>
       </c>
       <c r="G60">
         <v>279.1</v>
@@ -6207,28 +6207,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M60">
-        <v>38.1255808</v>
+        <v>38.78291840000001</v>
       </c>
       <c r="N60">
-        <v>42.2744192</v>
+        <v>41.6170816</v>
       </c>
       <c r="O60">
-        <v>10.5686048</v>
+        <v>10.4042704</v>
       </c>
       <c r="P60">
-        <v>31.7058144</v>
+        <v>31.2128112</v>
       </c>
       <c r="Q60">
-        <v>73.6058144</v>
+        <v>73.1128112</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1494337746949704</v>
+        <v>0.1516510142049184</v>
       </c>
       <c r="T60">
-        <v>2.020015162248376</v>
+        <v>2.063233287242993</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.108820333040015</v>
+        <v>2.073077615530862</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09571841582401658</v>
+        <v>0.09570164627614555</v>
       </c>
       <c r="C61">
-        <v>319.1485401595429</v>
+        <v>310.5445300169416</v>
       </c>
       <c r="D61">
-        <v>551.6965401595429</v>
+        <v>551.7645300169416</v>
       </c>
       <c r="E61">
-        <v>-24.55200000000002</v>
+        <v>-15.88</v>
       </c>
       <c r="F61">
-        <v>511.648</v>
+        <v>520.3200000000001</v>
       </c>
       <c r="G61">
         <v>279.1</v>
@@ -6289,28 +6289,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M61">
-        <v>38.78291840000001</v>
+        <v>39.44025600000001</v>
       </c>
       <c r="N61">
-        <v>41.6170816</v>
+        <v>40.959744</v>
       </c>
       <c r="O61">
-        <v>10.4042704</v>
+        <v>10.239936</v>
       </c>
       <c r="P61">
-        <v>31.2128112</v>
+        <v>30.719808</v>
       </c>
       <c r="Q61">
-        <v>73.1128112</v>
+        <v>72.61980800000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1516510142049184</v>
+        <v>0.1539791156903639</v>
       </c>
       <c r="T61">
-        <v>2.063233287242993</v>
+        <v>2.10861231848734</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.073077615530862</v>
+        <v>2.038526321938681</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09570164627614555</v>
+        <v>0.09568487672827454</v>
       </c>
       <c r="C62">
-        <v>310.5445300169416</v>
+        <v>301.9405366342442</v>
       </c>
       <c r="D62">
-        <v>551.7645300169416</v>
+        <v>551.8325366342441</v>
       </c>
       <c r="E62">
-        <v>-15.88</v>
+        <v>-7.208000000000084</v>
       </c>
       <c r="F62">
-        <v>520.3200000000001</v>
+        <v>528.992</v>
       </c>
       <c r="G62">
         <v>279.1</v>
@@ -6371,28 +6371,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M62">
-        <v>39.44025600000001</v>
+        <v>40.0975936</v>
       </c>
       <c r="N62">
-        <v>40.959744</v>
+        <v>40.3024064</v>
       </c>
       <c r="O62">
-        <v>10.239936</v>
+        <v>10.0756016</v>
       </c>
       <c r="P62">
-        <v>30.719808</v>
+        <v>30.2268048</v>
       </c>
       <c r="Q62">
-        <v>72.61980800000001</v>
+        <v>72.1268048</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1539791156903639</v>
+        <v>0.1564266069955757</v>
       </c>
       <c r="T62">
-        <v>2.10861231848734</v>
+        <v>2.15631847953909</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.038526321938681</v>
+        <v>2.005107857644604</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09568487672827454</v>
+        <v>0.1022711071804035</v>
       </c>
       <c r="C63">
-        <v>301.9405366342442</v>
+        <v>267.7890816725732</v>
       </c>
       <c r="D63">
-        <v>551.8325366342441</v>
+        <v>526.3530816725731</v>
       </c>
       <c r="E63">
-        <v>-7.208000000000084</v>
+        <v>1.463999999999942</v>
       </c>
       <c r="F63">
-        <v>528.992</v>
+        <v>537.664</v>
       </c>
       <c r="G63">
         <v>279.1</v>
@@ -6453,45 +6453,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M63">
-        <v>40.0975936</v>
+        <v>48.38976</v>
       </c>
       <c r="N63">
-        <v>40.3024064</v>
+        <v>32.01024000000001</v>
       </c>
       <c r="O63">
-        <v>10.0756016</v>
+        <v>8.002560000000003</v>
       </c>
       <c r="P63">
-        <v>30.2268048</v>
+        <v>24.00768000000001</v>
       </c>
       <c r="Q63">
-        <v>72.1268048</v>
+        <v>65.90768</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1564266069955757</v>
+        <v>0.1590029136326409</v>
       </c>
       <c r="T63">
-        <v>2.15631847953909</v>
+        <v>2.206535491172511</v>
       </c>
       <c r="U63">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.005107857644604</v>
+        <v>1.661508550569377</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1022711071804035</v>
+        <v>0.1023608376325325</v>
       </c>
       <c r="C64">
-        <v>267.7890816725732</v>
+        <v>258.7861869609656</v>
       </c>
       <c r="D64">
-        <v>526.3530816725731</v>
+        <v>526.0221869609655</v>
       </c>
       <c r="E64">
-        <v>1.463999999999942</v>
+        <v>10.13599999999997</v>
       </c>
       <c r="F64">
-        <v>537.664</v>
+        <v>546.336</v>
       </c>
       <c r="G64">
         <v>279.1</v>
@@ -6535,28 +6535,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M64">
-        <v>48.38976</v>
+        <v>49.17024</v>
       </c>
       <c r="N64">
-        <v>32.01024000000001</v>
+        <v>31.22976000000001</v>
       </c>
       <c r="O64">
-        <v>8.002560000000003</v>
+        <v>7.807440000000001</v>
       </c>
       <c r="P64">
-        <v>24.00768000000001</v>
+        <v>23.42232000000001</v>
       </c>
       <c r="Q64">
-        <v>65.90768</v>
+        <v>65.32232</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1590029136326409</v>
+        <v>0.1617184800879257</v>
       </c>
       <c r="T64">
-        <v>2.206535491172511</v>
+        <v>2.259466935867198</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.661508550569377</v>
+        <v>1.635135398973038</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1023608376325325</v>
+        <v>0.1024505680846615</v>
       </c>
       <c r="C65">
-        <v>258.7861869609656</v>
+        <v>249.7837080254782</v>
       </c>
       <c r="D65">
-        <v>526.0221869609655</v>
+        <v>525.6917080254782</v>
       </c>
       <c r="E65">
-        <v>10.13599999999997</v>
+        <v>18.80799999999999</v>
       </c>
       <c r="F65">
-        <v>546.336</v>
+        <v>555.008</v>
       </c>
       <c r="G65">
         <v>279.1</v>
@@ -6617,28 +6617,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M65">
-        <v>49.17024</v>
+        <v>49.95072</v>
       </c>
       <c r="N65">
-        <v>31.22976000000001</v>
+        <v>30.44928</v>
       </c>
       <c r="O65">
-        <v>7.807440000000001</v>
+        <v>7.61232</v>
       </c>
       <c r="P65">
-        <v>23.42232000000001</v>
+        <v>22.83696</v>
       </c>
       <c r="Q65">
-        <v>65.32232</v>
+        <v>64.73696</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1617184800879257</v>
+        <v>0.1645849113462819</v>
       </c>
       <c r="T65">
-        <v>2.259466935867198</v>
+        <v>2.315339016378256</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.635135398973038</v>
+        <v>1.609586408364084</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1024505680846615</v>
+        <v>0.1025402985367905</v>
       </c>
       <c r="C66">
-        <v>249.7837080254782</v>
+        <v>240.7816440829561</v>
       </c>
       <c r="D66">
-        <v>525.6917080254782</v>
+        <v>525.3616440829561</v>
       </c>
       <c r="E66">
-        <v>18.80799999999999</v>
+        <v>27.48000000000002</v>
       </c>
       <c r="F66">
-        <v>555.008</v>
+        <v>563.6800000000001</v>
       </c>
       <c r="G66">
         <v>279.1</v>
@@ -6699,28 +6699,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M66">
-        <v>49.95072</v>
+        <v>50.7312</v>
       </c>
       <c r="N66">
-        <v>30.44928</v>
+        <v>29.6688</v>
       </c>
       <c r="O66">
-        <v>7.61232</v>
+        <v>7.417200000000001</v>
       </c>
       <c r="P66">
-        <v>22.83696</v>
+        <v>22.2516</v>
       </c>
       <c r="Q66">
-        <v>64.73696</v>
+        <v>64.1516</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1645849113462819</v>
+        <v>0.1676151386765442</v>
       </c>
       <c r="T66">
-        <v>2.315339016378256</v>
+        <v>2.374403787204233</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.609586408364084</v>
+        <v>1.584823540543098</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1025402985367905</v>
+        <v>0.1026300289889195</v>
       </c>
       <c r="C67">
-        <v>240.7816440829561</v>
+        <v>231.7799943522098</v>
       </c>
       <c r="D67">
-        <v>525.3616440829561</v>
+        <v>525.0319943522098</v>
       </c>
       <c r="E67">
-        <v>27.48000000000002</v>
+        <v>36.15200000000004</v>
       </c>
       <c r="F67">
-        <v>563.6800000000001</v>
+        <v>572.3520000000001</v>
       </c>
       <c r="G67">
         <v>279.1</v>
@@ -6781,28 +6781,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M67">
-        <v>50.7312</v>
+        <v>51.51168000000001</v>
       </c>
       <c r="N67">
-        <v>29.6688</v>
+        <v>28.88832</v>
       </c>
       <c r="O67">
-        <v>7.417200000000001</v>
+        <v>7.22208</v>
       </c>
       <c r="P67">
-        <v>22.2516</v>
+        <v>21.66624</v>
       </c>
       <c r="Q67">
-        <v>64.1516</v>
+        <v>63.56624</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1676151386765442</v>
+        <v>0.1708236146732925</v>
       </c>
       <c r="T67">
-        <v>2.374403787204233</v>
+        <v>2.436942956314089</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.584823540543098</v>
+        <v>1.560811062656081</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1026300289889195</v>
+        <v>0.1027197594410484</v>
       </c>
       <c r="C68">
-        <v>231.7799943522098</v>
+        <v>222.7787580540095</v>
       </c>
       <c r="D68">
-        <v>525.0319943522098</v>
+        <v>524.7027580540096</v>
       </c>
       <c r="E68">
-        <v>36.15200000000004</v>
+        <v>44.82400000000007</v>
       </c>
       <c r="F68">
-        <v>572.3520000000001</v>
+        <v>581.0240000000001</v>
       </c>
       <c r="G68">
         <v>279.1</v>
@@ -6863,28 +6863,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M68">
-        <v>51.51168000000001</v>
+        <v>52.29216000000001</v>
       </c>
       <c r="N68">
-        <v>28.88832</v>
+        <v>28.10784</v>
       </c>
       <c r="O68">
-        <v>7.22208</v>
+        <v>7.026959999999999</v>
       </c>
       <c r="P68">
-        <v>21.66624</v>
+        <v>21.08088</v>
       </c>
       <c r="Q68">
-        <v>63.56624</v>
+        <v>62.98088</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1708236146732925</v>
+        <v>0.1742265437607529</v>
       </c>
       <c r="T68">
-        <v>2.436942956314089</v>
+        <v>2.503272378097271</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.560811062656081</v>
+        <v>1.537515375153751</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1027197594410484</v>
+        <v>0.1028094898931774</v>
       </c>
       <c r="C69">
-        <v>222.7787580540095</v>
+        <v>213.7779344110786</v>
       </c>
       <c r="D69">
-        <v>524.7027580540096</v>
+        <v>524.3739344110786</v>
       </c>
       <c r="E69">
-        <v>44.82400000000007</v>
+        <v>53.49599999999998</v>
       </c>
       <c r="F69">
-        <v>581.0240000000001</v>
+        <v>589.696</v>
       </c>
       <c r="G69">
         <v>279.1</v>
@@ -6945,28 +6945,28 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M69">
-        <v>52.29216000000001</v>
+        <v>53.07264</v>
       </c>
       <c r="N69">
-        <v>28.10784</v>
+        <v>27.32736000000001</v>
       </c>
       <c r="O69">
-        <v>7.026959999999999</v>
+        <v>6.831840000000001</v>
       </c>
       <c r="P69">
-        <v>21.08088</v>
+        <v>20.49552000000001</v>
       </c>
       <c r="Q69">
-        <v>62.98088</v>
+        <v>62.39552</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1742265437607529</v>
+        <v>0.1778421559161795</v>
       </c>
       <c r="T69">
-        <v>2.503272378097271</v>
+        <v>2.573747388741901</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.537515375153751</v>
+        <v>1.514904854930902</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1028094898931774</v>
+        <v>0.1351820113363388</v>
       </c>
       <c r="C70">
-        <v>213.7779344110786</v>
+        <v>108.4108976997829</v>
       </c>
       <c r="D70">
-        <v>524.3739344110786</v>
+        <v>427.678897699783</v>
       </c>
       <c r="E70">
-        <v>53.49599999999998</v>
+        <v>62.16800000000001</v>
       </c>
       <c r="F70">
-        <v>589.696</v>
+        <v>598.3680000000001</v>
       </c>
       <c r="G70">
         <v>279.1</v>
@@ -7027,45 +7027,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M70">
-        <v>53.07264</v>
+        <v>87.84042240000002</v>
       </c>
       <c r="N70">
-        <v>27.32736000000001</v>
+        <v>-7.440422400000017</v>
       </c>
       <c r="O70">
-        <v>6.831840000000001</v>
+        <v>-1.860105600000004</v>
       </c>
       <c r="P70">
-        <v>20.49552000000001</v>
+        <v>-5.580316800000013</v>
       </c>
       <c r="Q70">
-        <v>62.39552</v>
+        <v>36.31968319999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1778421559161795</v>
+        <v>0.1840905019896181</v>
       </c>
       <c r="T70">
-        <v>2.573747388741901</v>
+        <v>2.69553928375365</v>
       </c>
       <c r="U70">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.25</v>
+        <v>0.2288240362560005</v>
       </c>
       <c r="W70">
-        <v>0.0675</v>
+        <v>0.1132086314776191</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.514904854930902</v>
+        <v>0.9152961450240019</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1351820113363388</v>
+        <v>0.1361920113363388</v>
       </c>
       <c r="C71">
-        <v>108.4108976997829</v>
+        <v>97.29245898180886</v>
       </c>
       <c r="D71">
-        <v>427.678897699783</v>
+        <v>425.232458981809</v>
       </c>
       <c r="E71">
-        <v>62.16800000000001</v>
+        <v>70.84000000000003</v>
       </c>
       <c r="F71">
-        <v>598.3680000000001</v>
+        <v>607.0400000000001</v>
       </c>
       <c r="G71">
         <v>279.1</v>
@@ -7109,37 +7109,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M71">
-        <v>87.84042240000002</v>
+        <v>89.11347200000002</v>
       </c>
       <c r="N71">
-        <v>-7.440422400000017</v>
+        <v>-8.71347200000001</v>
       </c>
       <c r="O71">
-        <v>-1.860105600000004</v>
+        <v>-2.178368000000003</v>
       </c>
       <c r="P71">
-        <v>-5.580316800000013</v>
+        <v>-6.535104000000008</v>
       </c>
       <c r="Q71">
-        <v>36.31968319999999</v>
+        <v>35.36489599999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1840905019896181</v>
+        <v>0.188700185389272</v>
       </c>
       <c r="T71">
-        <v>2.69553928375365</v>
+        <v>2.785390593212105</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2288240362560005</v>
+        <v>0.2255551214523434</v>
       </c>
       <c r="W71">
-        <v>0.1132086314776191</v>
+        <v>0.113688508170796</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9152961450240019</v>
+        <v>0.9022204858093734</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1361920113363388</v>
+        <v>0.1372020113363388</v>
       </c>
       <c r="C72">
-        <v>97.29245898180886</v>
+        <v>86.20184965166231</v>
       </c>
       <c r="D72">
-        <v>425.232458981809</v>
+        <v>422.8138496516624</v>
       </c>
       <c r="E72">
-        <v>70.84000000000003</v>
+        <v>79.51200000000006</v>
       </c>
       <c r="F72">
-        <v>607.0400000000001</v>
+        <v>615.7120000000001</v>
       </c>
       <c r="G72">
         <v>279.1</v>
@@ -7191,37 +7191,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M72">
-        <v>89.11347200000002</v>
+        <v>90.38652160000002</v>
       </c>
       <c r="N72">
-        <v>-8.71347200000001</v>
+        <v>-9.986521600000017</v>
       </c>
       <c r="O72">
-        <v>-2.178368000000003</v>
+        <v>-2.496630400000004</v>
       </c>
       <c r="P72">
-        <v>-6.535104000000008</v>
+        <v>-7.489891200000013</v>
       </c>
       <c r="Q72">
-        <v>35.36489599999999</v>
+        <v>34.41010879999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.188700185389272</v>
+        <v>0.1936277779889021</v>
       </c>
       <c r="T72">
-        <v>2.785390593212105</v>
+        <v>2.881438544702179</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2255551214523434</v>
+        <v>0.2223782887558315</v>
       </c>
       <c r="W72">
-        <v>0.113688508170796</v>
+        <v>0.114154867210644</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9022204858093734</v>
+        <v>0.8895131550233257</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1372020113363388</v>
+        <v>0.1382120113363388</v>
       </c>
       <c r="C73">
-        <v>86.20184965166243</v>
+        <v>75.13859753642919</v>
       </c>
       <c r="D73">
-        <v>422.8138496516624</v>
+        <v>420.4225975364291</v>
       </c>
       <c r="E73">
-        <v>79.51199999999994</v>
+        <v>88.18399999999997</v>
       </c>
       <c r="F73">
-        <v>615.712</v>
+        <v>624.384</v>
       </c>
       <c r="G73">
         <v>279.1</v>
@@ -7273,37 +7273,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M73">
-        <v>90.38652160000001</v>
+        <v>91.65957120000002</v>
       </c>
       <c r="N73">
-        <v>-9.986521600000003</v>
+        <v>-11.25957120000001</v>
       </c>
       <c r="O73">
-        <v>-2.496630400000001</v>
+        <v>-2.814892800000003</v>
       </c>
       <c r="P73">
-        <v>-7.489891200000002</v>
+        <v>-8.444678400000008</v>
       </c>
       <c r="Q73">
-        <v>34.4101088</v>
+        <v>33.45532159999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.193627777988902</v>
+        <v>0.1989073414885057</v>
       </c>
       <c r="T73">
-        <v>2.881438544702177</v>
+        <v>2.984347064155827</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2223782887558315</v>
+        <v>0.2192897014120005</v>
       </c>
       <c r="W73">
-        <v>0.114154867210644</v>
+        <v>0.1146082718327184</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.889513155023326</v>
+        <v>0.8771588056480019</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1382120113363388</v>
+        <v>0.1392220113363388</v>
       </c>
       <c r="C74">
-        <v>75.13859753642919</v>
+        <v>64.10224108474677</v>
       </c>
       <c r="D74">
-        <v>420.4225975364291</v>
+        <v>418.0582410847468</v>
       </c>
       <c r="E74">
-        <v>88.18399999999997</v>
+        <v>96.85599999999999</v>
       </c>
       <c r="F74">
-        <v>624.384</v>
+        <v>633.056</v>
       </c>
       <c r="G74">
         <v>279.1</v>
@@ -7355,37 +7355,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M74">
-        <v>91.65957120000002</v>
+        <v>92.93262080000001</v>
       </c>
       <c r="N74">
-        <v>-11.25957120000001</v>
+        <v>-12.5326208</v>
       </c>
       <c r="O74">
-        <v>-2.814892800000003</v>
+        <v>-3.133155200000001</v>
       </c>
       <c r="P74">
-        <v>-8.444678400000008</v>
+        <v>-9.399465600000003</v>
       </c>
       <c r="Q74">
-        <v>33.45532159999999</v>
+        <v>32.50053439999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1989073414885057</v>
+        <v>0.2045779837658577</v>
       </c>
       <c r="T74">
-        <v>2.984347064155827</v>
+        <v>3.094878436902338</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2192897014120005</v>
+        <v>0.2162857328995073</v>
       </c>
       <c r="W74">
-        <v>0.1146082718327184</v>
+        <v>0.1150492544103523</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8771588056480019</v>
+        <v>0.8651429315980294</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1392220113363388</v>
+        <v>0.1402320113363388</v>
       </c>
       <c r="C75">
-        <v>64.10224108474677</v>
+        <v>53.09232906980901</v>
       </c>
       <c r="D75">
-        <v>418.0582410847468</v>
+        <v>415.720329069809</v>
       </c>
       <c r="E75">
-        <v>96.85599999999999</v>
+        <v>105.528</v>
       </c>
       <c r="F75">
-        <v>633.056</v>
+        <v>641.7280000000001</v>
       </c>
       <c r="G75">
         <v>279.1</v>
@@ -7437,37 +7437,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M75">
-        <v>92.93262080000001</v>
+        <v>94.20567040000002</v>
       </c>
       <c r="N75">
-        <v>-12.5326208</v>
+        <v>-13.80567040000001</v>
       </c>
       <c r="O75">
-        <v>-3.133155200000001</v>
+        <v>-3.451417600000003</v>
       </c>
       <c r="P75">
-        <v>-9.399465600000003</v>
+        <v>-10.35425280000001</v>
       </c>
       <c r="Q75">
-        <v>32.50053439999999</v>
+        <v>31.54574719999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2045779837658577</v>
+        <v>0.2106848292953138</v>
       </c>
       <c r="T75">
-        <v>3.094878436902338</v>
+        <v>3.213912222937044</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2162857328995073</v>
+        <v>0.2133629527251897</v>
       </c>
       <c r="W75">
-        <v>0.1150492544103523</v>
+        <v>0.1154783185399422</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8651429315980294</v>
+        <v>0.8534518109007586</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1402320113363388</v>
+        <v>0.1412420113363388</v>
       </c>
       <c r="C76">
-        <v>53.09232906980901</v>
+        <v>42.10842030228105</v>
       </c>
       <c r="D76">
-        <v>415.720329069809</v>
+        <v>413.4084203022811</v>
       </c>
       <c r="E76">
-        <v>105.528</v>
+        <v>114.2</v>
       </c>
       <c r="F76">
-        <v>641.7280000000001</v>
+        <v>650.4000000000001</v>
       </c>
       <c r="G76">
         <v>279.1</v>
@@ -7519,37 +7519,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M76">
-        <v>94.20567040000002</v>
+        <v>95.47872000000002</v>
       </c>
       <c r="N76">
-        <v>-13.80567040000001</v>
+        <v>-15.07872000000002</v>
       </c>
       <c r="O76">
-        <v>-3.451417600000003</v>
+        <v>-3.769680000000005</v>
       </c>
       <c r="P76">
-        <v>-10.35425280000001</v>
+        <v>-11.30904000000001</v>
       </c>
       <c r="Q76">
-        <v>31.54574719999999</v>
+        <v>30.59095999999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2106848292953138</v>
+        <v>0.2172802224671264</v>
       </c>
       <c r="T76">
-        <v>3.213912222937044</v>
+        <v>3.342468711854526</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2133629527251897</v>
+        <v>0.2105181133555204</v>
       </c>
       <c r="W76">
-        <v>0.1154783185399422</v>
+        <v>0.1158959409594096</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8534518109007586</v>
+        <v>0.8420724534220818</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1412420113363388</v>
+        <v>0.1422520113363388</v>
       </c>
       <c r="C77">
-        <v>42.10842030228105</v>
+        <v>31.15008335274047</v>
       </c>
       <c r="D77">
-        <v>413.4084203022811</v>
+        <v>411.1220833527404</v>
       </c>
       <c r="E77">
-        <v>114.2</v>
+        <v>122.872</v>
       </c>
       <c r="F77">
-        <v>650.4000000000001</v>
+        <v>659.072</v>
       </c>
       <c r="G77">
         <v>279.1</v>
@@ -7601,37 +7601,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M77">
-        <v>95.47872000000002</v>
+        <v>96.7517696</v>
       </c>
       <c r="N77">
-        <v>-15.07872000000002</v>
+        <v>-16.3517696</v>
       </c>
       <c r="O77">
-        <v>-3.769680000000005</v>
+        <v>-4.087942399999999</v>
       </c>
       <c r="P77">
-        <v>-11.30904000000001</v>
+        <v>-12.2638272</v>
       </c>
       <c r="Q77">
-        <v>30.59095999999998</v>
+        <v>29.6361728</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2172802224671264</v>
+        <v>0.22442523173659</v>
       </c>
       <c r="T77">
-        <v>3.342468711854526</v>
+        <v>3.481738241515131</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2105181133555204</v>
+        <v>0.20774813817979</v>
       </c>
       <c r="W77">
-        <v>0.1158959409594096</v>
+        <v>0.1163025733152068</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8420724534220818</v>
+        <v>0.8309925527191598</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1422520113363388</v>
+        <v>0.1432620113363388</v>
       </c>
       <c r="C78">
-        <v>31.15008335274047</v>
+        <v>20.21689628327704</v>
       </c>
       <c r="D78">
-        <v>411.1220833527404</v>
+        <v>408.860896283277</v>
       </c>
       <c r="E78">
-        <v>122.872</v>
+        <v>131.544</v>
       </c>
       <c r="F78">
-        <v>659.072</v>
+        <v>667.744</v>
       </c>
       <c r="G78">
         <v>279.1</v>
@@ -7683,37 +7683,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M78">
-        <v>96.7517696</v>
+        <v>98.02481920000001</v>
       </c>
       <c r="N78">
-        <v>-16.3517696</v>
+        <v>-17.6248192</v>
       </c>
       <c r="O78">
-        <v>-4.087942399999999</v>
+        <v>-4.406204800000001</v>
       </c>
       <c r="P78">
-        <v>-12.2638272</v>
+        <v>-13.2186144</v>
       </c>
       <c r="Q78">
-        <v>29.6361728</v>
+        <v>28.6813856</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.22442523173659</v>
+        <v>0.23219154615992</v>
       </c>
       <c r="T78">
-        <v>3.481738241515131</v>
+        <v>3.633118165059267</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.20774813817979</v>
+        <v>0.2050501104112212</v>
       </c>
       <c r="W78">
-        <v>0.1163025733152068</v>
+        <v>0.1166986437916327</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8309925527191598</v>
+        <v>0.8202004416448849</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1432620113363388</v>
+        <v>0.1442720113363388</v>
       </c>
       <c r="C79">
-        <v>20.21689628327704</v>
+        <v>9.308446387903473</v>
       </c>
       <c r="D79">
-        <v>408.860896283277</v>
+        <v>406.6244463879034</v>
       </c>
       <c r="E79">
-        <v>131.544</v>
+        <v>140.216</v>
       </c>
       <c r="F79">
-        <v>667.744</v>
+        <v>676.4160000000001</v>
       </c>
       <c r="G79">
         <v>279.1</v>
@@ -7765,37 +7765,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M79">
-        <v>98.02481920000001</v>
+        <v>99.29786880000002</v>
       </c>
       <c r="N79">
-        <v>-17.6248192</v>
+        <v>-18.89786880000001</v>
       </c>
       <c r="O79">
-        <v>-4.406204800000001</v>
+        <v>-4.724467200000003</v>
       </c>
       <c r="P79">
-        <v>-13.2186144</v>
+        <v>-14.17340160000001</v>
       </c>
       <c r="Q79">
-        <v>28.6813856</v>
+        <v>27.72659839999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.23219154615992</v>
+        <v>0.2406638891671891</v>
       </c>
       <c r="T79">
-        <v>3.633118165059267</v>
+        <v>3.798259899834689</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2050501104112212</v>
+        <v>0.2024212628418466</v>
       </c>
       <c r="W79">
-        <v>0.1166986437916327</v>
+        <v>0.1170845586148169</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8202004416448849</v>
+        <v>0.8096850513673863</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1442720113363388</v>
+        <v>0.1901035612900627</v>
       </c>
       <c r="C80">
-        <v>9.308446387903473</v>
+        <v>-80.22306353689157</v>
       </c>
       <c r="D80">
-        <v>406.6244463879034</v>
+        <v>325.7649364631085</v>
       </c>
       <c r="E80">
-        <v>140.216</v>
+        <v>148.888</v>
       </c>
       <c r="F80">
-        <v>676.4160000000001</v>
+        <v>685.0880000000001</v>
       </c>
       <c r="G80">
         <v>279.1</v>
@@ -7847,45 +7847,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M80">
-        <v>99.29786880000002</v>
+        <v>137.5656704</v>
       </c>
       <c r="N80">
-        <v>-18.89786880000001</v>
+        <v>-57.16567040000001</v>
       </c>
       <c r="O80">
-        <v>-4.724467200000003</v>
+        <v>-14.2914176</v>
       </c>
       <c r="P80">
-        <v>-14.17340160000001</v>
+        <v>-42.87425280000001</v>
       </c>
       <c r="Q80">
-        <v>27.72659839999999</v>
+        <v>-0.9742528000000092</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2406638891671891</v>
+        <v>0.2602362170024068</v>
       </c>
       <c r="T80">
-        <v>3.798259899834689</v>
+        <v>4.179760999297725</v>
       </c>
       <c r="U80">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.2024212628418466</v>
+        <v>0.1461120346490166</v>
       </c>
       <c r="W80">
-        <v>0.1170845586148169</v>
+        <v>0.1714607034424775</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8096850513673863</v>
+        <v>0.5844481385960665</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1901035612900627</v>
+        <v>0.1916535612900626</v>
       </c>
       <c r="C81">
-        <v>-80.22306353689157</v>
+        <v>-91.07126036901093</v>
       </c>
       <c r="D81">
-        <v>325.7649364631085</v>
+        <v>323.5887396309891</v>
       </c>
       <c r="E81">
-        <v>148.888</v>
+        <v>157.5600000000001</v>
       </c>
       <c r="F81">
-        <v>685.0880000000001</v>
+        <v>693.7600000000001</v>
       </c>
       <c r="G81">
         <v>279.1</v>
@@ -7929,37 +7929,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M81">
-        <v>137.5656704</v>
+        <v>139.307008</v>
       </c>
       <c r="N81">
-        <v>-57.16567040000001</v>
+        <v>-58.90700800000002</v>
       </c>
       <c r="O81">
-        <v>-14.2914176</v>
+        <v>-14.726752</v>
       </c>
       <c r="P81">
-        <v>-42.87425280000001</v>
+        <v>-44.18025600000001</v>
       </c>
       <c r="Q81">
-        <v>-0.9742528000000092</v>
+        <v>-2.280256000000016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2602362170024068</v>
+        <v>0.2709580278525272</v>
       </c>
       <c r="T81">
-        <v>4.179760999297725</v>
+        <v>4.388749049262612</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1461120346490166</v>
+        <v>0.1442856342159039</v>
       </c>
       <c r="W81">
-        <v>0.1714607034424775</v>
+        <v>0.1718274446494465</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5844481385960665</v>
+        <v>0.5771425368636156</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1916535612900626</v>
+        <v>0.1932035612900626</v>
       </c>
       <c r="C82">
-        <v>-91.07126036901093</v>
+        <v>-101.8905749892253</v>
       </c>
       <c r="D82">
-        <v>323.5887396309891</v>
+        <v>321.4414250107748</v>
       </c>
       <c r="E82">
-        <v>157.5600000000001</v>
+        <v>166.2320000000001</v>
       </c>
       <c r="F82">
-        <v>693.7600000000001</v>
+        <v>702.4320000000001</v>
       </c>
       <c r="G82">
         <v>279.1</v>
@@ -8011,37 +8011,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M82">
-        <v>139.307008</v>
+        <v>141.0483456</v>
       </c>
       <c r="N82">
-        <v>-58.90700800000002</v>
+        <v>-60.64834560000003</v>
       </c>
       <c r="O82">
-        <v>-14.726752</v>
+        <v>-15.16208640000001</v>
       </c>
       <c r="P82">
-        <v>-44.18025600000001</v>
+        <v>-45.48625920000002</v>
       </c>
       <c r="Q82">
-        <v>-2.280256000000016</v>
+        <v>-3.586259200000022</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2709580278525272</v>
+        <v>0.2828084503710813</v>
       </c>
       <c r="T82">
-        <v>4.388749049262612</v>
+        <v>4.619735841329065</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1442856342159039</v>
+        <v>0.1425043300897816</v>
       </c>
       <c r="W82">
-        <v>0.1718274446494465</v>
+        <v>0.1721851305179719</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5771425368636156</v>
+        <v>0.5700173203591266</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1932035612900626</v>
+        <v>0.1947535612900627</v>
       </c>
       <c r="C83">
-        <v>-101.8905749892253</v>
+        <v>-112.6815785887958</v>
       </c>
       <c r="D83">
-        <v>321.4414250107748</v>
+        <v>319.3224214112042</v>
       </c>
       <c r="E83">
-        <v>166.2320000000001</v>
+        <v>174.904</v>
       </c>
       <c r="F83">
-        <v>702.4320000000001</v>
+        <v>711.104</v>
       </c>
       <c r="G83">
         <v>279.1</v>
@@ -8093,37 +8093,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M83">
-        <v>141.0483456</v>
+        <v>142.7896832</v>
       </c>
       <c r="N83">
-        <v>-60.64834560000003</v>
+        <v>-62.38968320000001</v>
       </c>
       <c r="O83">
-        <v>-15.16208640000001</v>
+        <v>-15.5974208</v>
       </c>
       <c r="P83">
-        <v>-45.48625920000002</v>
+        <v>-46.79226240000001</v>
       </c>
       <c r="Q83">
-        <v>-3.586259200000022</v>
+        <v>-4.892262400000007</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2828084503710813</v>
+        <v>0.295975586502808</v>
       </c>
       <c r="T83">
-        <v>4.619735841329065</v>
+        <v>4.876387832514014</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1425043300897816</v>
+        <v>0.1407664724057599</v>
       </c>
       <c r="W83">
-        <v>0.1721851305179719</v>
+        <v>0.1725340923409234</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5700173203591266</v>
+        <v>0.5630658896230396</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1947535612900627</v>
+        <v>0.1963035612900627</v>
       </c>
       <c r="C84">
-        <v>-112.6815785887958</v>
+        <v>-123.4448273960124</v>
       </c>
       <c r="D84">
-        <v>319.3224214112042</v>
+        <v>317.2311726039876</v>
       </c>
       <c r="E84">
-        <v>174.904</v>
+        <v>183.576</v>
       </c>
       <c r="F84">
-        <v>711.104</v>
+        <v>719.7760000000001</v>
       </c>
       <c r="G84">
         <v>279.1</v>
@@ -8175,37 +8175,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M84">
-        <v>142.7896832</v>
+        <v>144.5310208</v>
       </c>
       <c r="N84">
-        <v>-62.38968320000001</v>
+        <v>-64.13102080000002</v>
       </c>
       <c r="O84">
-        <v>-15.5974208</v>
+        <v>-16.0327552</v>
       </c>
       <c r="P84">
-        <v>-46.79226240000001</v>
+        <v>-48.09826560000001</v>
       </c>
       <c r="Q84">
-        <v>-4.892262400000007</v>
+        <v>-6.198265600000013</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.295975586502808</v>
+        <v>0.3106917974735615</v>
       </c>
       <c r="T84">
-        <v>4.876387832514014</v>
+        <v>5.163234175603074</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1407664724057599</v>
+        <v>0.1390704908105098</v>
       </c>
       <c r="W84">
-        <v>0.1725340923409234</v>
+        <v>0.1728746454452496</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5630658896230396</v>
+        <v>0.5562819632420392</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1963035612900627</v>
+        <v>0.1978535612900627</v>
       </c>
       <c r="C85">
-        <v>-123.4448273960124</v>
+        <v>-134.1808631629704</v>
       </c>
       <c r="D85">
-        <v>317.2311726039876</v>
+        <v>315.1671368370298</v>
       </c>
       <c r="E85">
-        <v>183.576</v>
+        <v>192.248</v>
       </c>
       <c r="F85">
-        <v>719.7760000000001</v>
+        <v>728.4480000000001</v>
       </c>
       <c r="G85">
         <v>279.1</v>
@@ -8257,37 +8257,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M85">
-        <v>144.5310208</v>
+        <v>146.2723584</v>
       </c>
       <c r="N85">
-        <v>-64.13102080000002</v>
+        <v>-65.87235840000002</v>
       </c>
       <c r="O85">
-        <v>-16.0327552</v>
+        <v>-16.46808960000001</v>
       </c>
       <c r="P85">
-        <v>-48.09826560000001</v>
+        <v>-49.40426880000002</v>
       </c>
       <c r="Q85">
-        <v>-6.198265600000013</v>
+        <v>-7.50426880000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3106917974735615</v>
+        <v>0.3272475348156591</v>
       </c>
       <c r="T85">
-        <v>5.163234175603074</v>
+        <v>5.485936311578267</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1390704908105098</v>
+        <v>0.1374148897294323</v>
       </c>
       <c r="W85">
-        <v>0.1728746454452496</v>
+        <v>0.17320709014233</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5562819632420392</v>
+        <v>0.5496595589177291</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1978535612900627</v>
+        <v>0.1994035612900626</v>
       </c>
       <c r="C86">
-        <v>-134.1808631629702</v>
+        <v>-144.8902136334651</v>
       </c>
       <c r="D86">
-        <v>315.1671368370298</v>
+        <v>313.1297863665348</v>
       </c>
       <c r="E86">
-        <v>192.2479999999999</v>
+        <v>200.92</v>
       </c>
       <c r="F86">
-        <v>728.448</v>
+        <v>737.12</v>
       </c>
       <c r="G86">
         <v>279.1</v>
@@ -8339,37 +8339,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M86">
-        <v>146.2723584</v>
+        <v>148.013696</v>
       </c>
       <c r="N86">
-        <v>-65.8723584</v>
+        <v>-67.613696</v>
       </c>
       <c r="O86">
-        <v>-16.4680896</v>
+        <v>-16.903424</v>
       </c>
       <c r="P86">
-        <v>-49.4042688</v>
+        <v>-50.710272</v>
       </c>
       <c r="Q86">
-        <v>-7.504268799999998</v>
+        <v>-8.810272000000005</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3272475348156589</v>
+        <v>0.3460107038033696</v>
       </c>
       <c r="T86">
-        <v>5.485936311578263</v>
+        <v>5.851665399016815</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1374148897294323</v>
+        <v>0.1357982439679096</v>
       </c>
       <c r="W86">
-        <v>0.17320709014233</v>
+        <v>0.1735317126112438</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5496595589177292</v>
+        <v>0.5431929758716383</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1994035612900626</v>
+        <v>0.2009535612900626</v>
       </c>
       <c r="C87">
-        <v>-144.8902136334651</v>
+        <v>-155.5733929928585</v>
       </c>
       <c r="D87">
-        <v>313.1297863665348</v>
+        <v>311.1186070071415</v>
       </c>
       <c r="E87">
-        <v>200.92</v>
+        <v>209.592</v>
       </c>
       <c r="F87">
-        <v>737.12</v>
+        <v>745.792</v>
       </c>
       <c r="G87">
         <v>279.1</v>
@@ -8421,37 +8421,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M87">
-        <v>148.013696</v>
+        <v>149.7550336</v>
       </c>
       <c r="N87">
-        <v>-67.613696</v>
+        <v>-69.35503360000001</v>
       </c>
       <c r="O87">
-        <v>-16.903424</v>
+        <v>-17.3387584</v>
       </c>
       <c r="P87">
-        <v>-50.710272</v>
+        <v>-52.01627520000001</v>
       </c>
       <c r="Q87">
-        <v>-8.810272000000005</v>
+        <v>-10.11627520000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3460107038033696</v>
+        <v>0.3674543255036102</v>
       </c>
       <c r="T87">
-        <v>5.851665399016815</v>
+        <v>6.269641498946586</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1357982439679096</v>
+        <v>0.1342191946194455</v>
       </c>
       <c r="W87">
-        <v>0.1735317126112438</v>
+        <v>0.1738487857204153</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5431929758716383</v>
+        <v>0.5368767784777819</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2009535612900626</v>
+        <v>0.2025035612900626</v>
       </c>
       <c r="C88">
-        <v>-155.5733929928585</v>
+        <v>-166.2309023007159</v>
       </c>
       <c r="D88">
-        <v>311.1186070071415</v>
+        <v>309.1330976992842</v>
       </c>
       <c r="E88">
-        <v>209.592</v>
+        <v>218.264</v>
       </c>
       <c r="F88">
-        <v>745.792</v>
+        <v>754.4640000000001</v>
       </c>
       <c r="G88">
         <v>279.1</v>
@@ -8503,37 +8503,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M88">
-        <v>149.7550336</v>
+        <v>151.4963712</v>
       </c>
       <c r="N88">
-        <v>-69.35503360000001</v>
+        <v>-71.09637120000002</v>
       </c>
       <c r="O88">
-        <v>-17.3387584</v>
+        <v>-17.77409280000001</v>
       </c>
       <c r="P88">
-        <v>-52.01627520000001</v>
+        <v>-53.32227840000002</v>
       </c>
       <c r="Q88">
-        <v>-10.11627520000001</v>
+        <v>-11.42227840000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3674543255036102</v>
+        <v>0.3921969659269648</v>
       </c>
       <c r="T88">
-        <v>6.269641498946586</v>
+        <v>6.751921614250169</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1342191946194455</v>
+        <v>0.1326764452560036</v>
       </c>
       <c r="W88">
-        <v>0.1738487857204153</v>
+        <v>0.1741585697925945</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5368767784777819</v>
+        <v>0.5307057810240143</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2025035612900626</v>
+        <v>0.2040535612900626</v>
       </c>
       <c r="C89">
-        <v>-166.2309023007159</v>
+        <v>-176.8632299069847</v>
       </c>
       <c r="D89">
-        <v>309.1330976992842</v>
+        <v>307.1727700930153</v>
       </c>
       <c r="E89">
-        <v>218.264</v>
+        <v>226.936</v>
       </c>
       <c r="F89">
-        <v>754.4640000000001</v>
+        <v>763.1360000000001</v>
       </c>
       <c r="G89">
         <v>279.1</v>
@@ -8585,37 +8585,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M89">
-        <v>151.4963712</v>
+        <v>153.2377088</v>
       </c>
       <c r="N89">
-        <v>-71.09637120000002</v>
+        <v>-72.8377088</v>
       </c>
       <c r="O89">
-        <v>-17.77409280000001</v>
+        <v>-18.2094272</v>
       </c>
       <c r="P89">
-        <v>-53.32227840000002</v>
+        <v>-54.6282816</v>
       </c>
       <c r="Q89">
-        <v>-11.42227840000002</v>
+        <v>-12.7282816</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3921969659269648</v>
+        <v>0.4210633797542119</v>
       </c>
       <c r="T89">
-        <v>6.751921614250169</v>
+        <v>7.314581748771018</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1326764452560036</v>
+        <v>0.1311687583780945</v>
       </c>
       <c r="W89">
-        <v>0.1741585697925945</v>
+        <v>0.1744613133176786</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5307057810240143</v>
+        <v>0.5246750335123779</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2040535612900626</v>
+        <v>0.2056035612900626</v>
       </c>
       <c r="C90">
-        <v>-176.8632299069847</v>
+        <v>-187.4708518524372</v>
       </c>
       <c r="D90">
-        <v>307.1727700930153</v>
+        <v>305.2371481475629</v>
       </c>
       <c r="E90">
-        <v>226.936</v>
+        <v>235.6080000000001</v>
       </c>
       <c r="F90">
-        <v>763.1360000000001</v>
+        <v>771.8080000000001</v>
       </c>
       <c r="G90">
         <v>279.1</v>
@@ -8667,37 +8667,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M90">
-        <v>153.2377088</v>
+        <v>154.9790464</v>
       </c>
       <c r="N90">
-        <v>-72.8377088</v>
+        <v>-74.57904640000001</v>
       </c>
       <c r="O90">
-        <v>-18.2094272</v>
+        <v>-18.6447616</v>
       </c>
       <c r="P90">
-        <v>-54.6282816</v>
+        <v>-55.93428480000001</v>
       </c>
       <c r="Q90">
-        <v>-12.7282816</v>
+        <v>-14.03428480000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4210633797542119</v>
+        <v>0.4551782324591403</v>
       </c>
       <c r="T90">
-        <v>7.314581748771018</v>
+        <v>7.97954372593202</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1311687583780945</v>
+        <v>0.1296949521041833</v>
       </c>
       <c r="W90">
-        <v>0.1744613133176786</v>
+        <v>0.17475725361748</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5246750335123779</v>
+        <v>0.5187798084167332</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2056035612900626</v>
+        <v>0.2071535612900626</v>
       </c>
       <c r="C91">
-        <v>-187.4708518524372</v>
+        <v>-198.0542322540673</v>
       </c>
       <c r="D91">
-        <v>305.2371481475629</v>
+        <v>303.3257677459326</v>
       </c>
       <c r="E91">
-        <v>235.6080000000001</v>
+        <v>244.28</v>
       </c>
       <c r="F91">
-        <v>771.8080000000001</v>
+        <v>780.48</v>
       </c>
       <c r="G91">
         <v>279.1</v>
@@ -8749,37 +8749,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M91">
-        <v>154.9790464</v>
+        <v>156.720384</v>
       </c>
       <c r="N91">
-        <v>-74.57904640000001</v>
+        <v>-76.32038399999999</v>
       </c>
       <c r="O91">
-        <v>-18.6447616</v>
+        <v>-19.080096</v>
       </c>
       <c r="P91">
-        <v>-55.93428480000001</v>
+        <v>-57.24028799999999</v>
       </c>
       <c r="Q91">
-        <v>-14.03428480000001</v>
+        <v>-15.34028799999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4551782324591403</v>
+        <v>0.4961160557050543</v>
       </c>
       <c r="T91">
-        <v>7.97954372593202</v>
+        <v>8.777498098525223</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1296949521041833</v>
+        <v>0.1282538970808035</v>
       </c>
       <c r="W91">
-        <v>0.17475725361748</v>
+        <v>0.1750466174661747</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5187798084167332</v>
+        <v>0.5130155883232139</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2071535612900626</v>
+        <v>0.2087035612900626</v>
       </c>
       <c r="C92">
-        <v>-198.0542322540673</v>
+        <v>-208.6138236760987</v>
       </c>
       <c r="D92">
-        <v>303.3257677459326</v>
+        <v>301.4381763239014</v>
       </c>
       <c r="E92">
-        <v>244.28</v>
+        <v>252.952</v>
       </c>
       <c r="F92">
-        <v>780.48</v>
+        <v>789.152</v>
       </c>
       <c r="G92">
         <v>279.1</v>
@@ -8831,37 +8831,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M92">
-        <v>156.720384</v>
+        <v>158.4617216</v>
       </c>
       <c r="N92">
-        <v>-76.32038399999999</v>
+        <v>-78.0617216</v>
       </c>
       <c r="O92">
-        <v>-19.080096</v>
+        <v>-19.5154304</v>
       </c>
       <c r="P92">
-        <v>-57.24028799999999</v>
+        <v>-58.5462912</v>
       </c>
       <c r="Q92">
-        <v>-15.34028799999999</v>
+        <v>-16.6462912</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4961160557050543</v>
+        <v>0.546151173005616</v>
       </c>
       <c r="T92">
-        <v>8.777498098525223</v>
+        <v>9.752775665028027</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1282538970808035</v>
+        <v>0.1268445135963991</v>
       </c>
       <c r="W92">
-        <v>0.1750466174661747</v>
+        <v>0.1753296216698431</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5130155883232139</v>
+        <v>0.5073780543855961</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2087035612900626</v>
+        <v>0.2102535612900626</v>
       </c>
       <c r="C93">
-        <v>-208.6138236760987</v>
+        <v>-219.1500674872245</v>
       </c>
       <c r="D93">
-        <v>301.4381763239014</v>
+        <v>299.5739325127756</v>
       </c>
       <c r="E93">
-        <v>252.952</v>
+        <v>261.624</v>
       </c>
       <c r="F93">
-        <v>789.152</v>
+        <v>797.8240000000001</v>
       </c>
       <c r="G93">
         <v>279.1</v>
@@ -8913,37 +8913,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M93">
-        <v>158.4617216</v>
+        <v>160.2030592</v>
       </c>
       <c r="N93">
-        <v>-78.0617216</v>
+        <v>-79.80305920000001</v>
       </c>
       <c r="O93">
-        <v>-19.5154304</v>
+        <v>-19.9507648</v>
       </c>
       <c r="P93">
-        <v>-58.5462912</v>
+        <v>-59.85229440000001</v>
       </c>
       <c r="Q93">
-        <v>-16.6462912</v>
+        <v>-17.95229440000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.546151173005616</v>
+        <v>0.6086950696313181</v>
       </c>
       <c r="T93">
-        <v>9.752775665028027</v>
+        <v>10.97187262315653</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1268445135963991</v>
+        <v>0.1254657688833947</v>
       </c>
       <c r="W93">
-        <v>0.1753296216698431</v>
+        <v>0.1756064736082144</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5073780543855961</v>
+        <v>0.5018630755335789</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2102535612900626</v>
+        <v>0.2452257728050183</v>
       </c>
       <c r="C94">
-        <v>-219.1500674872245</v>
+        <v>-264.5055578602803</v>
       </c>
       <c r="D94">
-        <v>299.5739325127756</v>
+        <v>262.8904421397198</v>
       </c>
       <c r="E94">
-        <v>261.624</v>
+        <v>270.296</v>
       </c>
       <c r="F94">
-        <v>797.8240000000001</v>
+        <v>806.4960000000001</v>
       </c>
       <c r="G94">
         <v>279.1</v>
@@ -8995,45 +8995,45 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M94">
-        <v>160.2030592</v>
+        <v>190.1717568</v>
       </c>
       <c r="N94">
-        <v>-79.80305920000001</v>
+        <v>-109.7717568</v>
       </c>
       <c r="O94">
-        <v>-19.9507648</v>
+        <v>-27.4429392</v>
       </c>
       <c r="P94">
-        <v>-59.85229440000001</v>
+        <v>-82.32881760000001</v>
       </c>
       <c r="Q94">
-        <v>-17.95229440000001</v>
+        <v>-40.42881760000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6086950696313181</v>
+        <v>0.701568815506587</v>
       </c>
       <c r="T94">
-        <v>10.97187262315653</v>
+        <v>12.78215479607782</v>
       </c>
       <c r="U94">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1254657688833947</v>
+        <v>0.1056939281532682</v>
       </c>
       <c r="W94">
-        <v>0.1756064736082144</v>
+        <v>0.2108773717414593</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5018630755335789</v>
+        <v>0.4227757126130729</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2452257728050183</v>
+        <v>0.2471257728050183</v>
       </c>
       <c r="C95">
-        <v>-264.5055578602803</v>
+        <v>-274.9149276876317</v>
       </c>
       <c r="D95">
-        <v>262.8904421397198</v>
+        <v>261.1530723123685</v>
       </c>
       <c r="E95">
-        <v>270.296</v>
+        <v>278.9680000000001</v>
       </c>
       <c r="F95">
-        <v>806.4960000000001</v>
+        <v>815.1680000000001</v>
       </c>
       <c r="G95">
         <v>279.1</v>
@@ -9077,37 +9077,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M95">
-        <v>190.1717568</v>
+        <v>192.2166144</v>
       </c>
       <c r="N95">
-        <v>-109.7717568</v>
+        <v>-111.8166144</v>
       </c>
       <c r="O95">
-        <v>-27.4429392</v>
+        <v>-27.95415360000001</v>
       </c>
       <c r="P95">
-        <v>-82.32881760000001</v>
+        <v>-83.86246080000001</v>
       </c>
       <c r="Q95">
-        <v>-40.42881760000001</v>
+        <v>-41.96246080000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.701568815506587</v>
+        <v>0.8108636180910185</v>
       </c>
       <c r="T95">
-        <v>12.78215479607782</v>
+        <v>14.91251392875746</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1056939281532682</v>
+        <v>0.104569524662276</v>
       </c>
       <c r="W95">
-        <v>0.2108773717414593</v>
+        <v>0.2111425060846353</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4227757126130729</v>
+        <v>0.418278098649104</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2471257728050183</v>
+        <v>0.2490257728050183</v>
       </c>
       <c r="C96">
-        <v>-274.9149276876317</v>
+        <v>-285.3014846904763</v>
       </c>
       <c r="D96">
-        <v>261.1530723123685</v>
+        <v>259.4385153095238</v>
       </c>
       <c r="E96">
-        <v>278.9680000000001</v>
+        <v>287.6400000000001</v>
       </c>
       <c r="F96">
-        <v>815.1680000000001</v>
+        <v>823.8400000000001</v>
       </c>
       <c r="G96">
         <v>279.1</v>
@@ -9159,37 +9159,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M96">
-        <v>192.2166144</v>
+        <v>194.2614720000001</v>
       </c>
       <c r="N96">
-        <v>-111.8166144</v>
+        <v>-113.861472</v>
       </c>
       <c r="O96">
-        <v>-27.95415360000001</v>
+        <v>-28.46536800000001</v>
       </c>
       <c r="P96">
-        <v>-83.86246080000001</v>
+        <v>-85.39610400000004</v>
       </c>
       <c r="Q96">
-        <v>-41.96246080000001</v>
+        <v>-43.49610400000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8108636180910185</v>
+        <v>0.9638763417092227</v>
       </c>
       <c r="T96">
-        <v>14.91251392875746</v>
+        <v>17.89501671450896</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.104569524662276</v>
+        <v>0.1034687928237257</v>
       </c>
       <c r="W96">
-        <v>0.2111425060846353</v>
+        <v>0.2114020586521655</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.418278098649104</v>
+        <v>0.4138751712949029</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2490257728050183</v>
+        <v>0.2509257728050183</v>
       </c>
       <c r="C97">
-        <v>-285.3014846904763</v>
+        <v>-295.6656752595103</v>
       </c>
       <c r="D97">
-        <v>259.4385153095238</v>
+        <v>257.7463247404898</v>
       </c>
       <c r="E97">
-        <v>287.6400000000001</v>
+        <v>296.312</v>
       </c>
       <c r="F97">
-        <v>823.8400000000001</v>
+        <v>832.5120000000001</v>
       </c>
       <c r="G97">
         <v>279.1</v>
@@ -9241,37 +9241,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M97">
-        <v>194.2614720000001</v>
+        <v>196.3063296</v>
       </c>
       <c r="N97">
-        <v>-113.861472</v>
+        <v>-115.9063296</v>
       </c>
       <c r="O97">
-        <v>-28.46536800000001</v>
+        <v>-28.97658240000001</v>
       </c>
       <c r="P97">
-        <v>-85.39610400000004</v>
+        <v>-86.92974720000001</v>
       </c>
       <c r="Q97">
-        <v>-43.49610400000004</v>
+        <v>-45.02974720000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9638763417092227</v>
+        <v>1.193395427136529</v>
       </c>
       <c r="T97">
-        <v>17.89501671450896</v>
+        <v>22.3687708931362</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1034687928237257</v>
+        <v>0.1023909928984786</v>
       </c>
       <c r="W97">
-        <v>0.2114020586521655</v>
+        <v>0.2116562038745387</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4138751712949029</v>
+        <v>0.4095639715939143</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2509257728050182</v>
+        <v>0.2528257728050183</v>
       </c>
       <c r="C98">
-        <v>-295.6656752595102</v>
+        <v>-306.0079342145482</v>
       </c>
       <c r="D98">
-        <v>257.7463247404899</v>
+        <v>256.0760657854518</v>
       </c>
       <c r="E98">
-        <v>296.312</v>
+        <v>304.9839999999999</v>
       </c>
       <c r="F98">
-        <v>832.5120000000001</v>
+        <v>841.184</v>
       </c>
       <c r="G98">
         <v>279.1</v>
@@ -9323,37 +9323,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M98">
-        <v>196.3063296</v>
+        <v>198.3511872</v>
       </c>
       <c r="N98">
-        <v>-115.9063296</v>
+        <v>-117.9511872</v>
       </c>
       <c r="O98">
-        <v>-28.97658240000001</v>
+        <v>-29.4877968</v>
       </c>
       <c r="P98">
-        <v>-86.92974720000001</v>
+        <v>-88.46339039999999</v>
       </c>
       <c r="Q98">
-        <v>-45.02974720000001</v>
+        <v>-46.5633904</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.193395427136525</v>
+        <v>1.575927236182034</v>
       </c>
       <c r="T98">
-        <v>22.36877089313614</v>
+        <v>29.82502785751486</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1023909928984786</v>
+        <v>0.1013354156521025</v>
       </c>
       <c r="W98">
-        <v>0.2116562038745387</v>
+        <v>0.2119051089892342</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4095639715939143</v>
+        <v>0.4053416626084102</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2528257728050183</v>
+        <v>0.2547257728050182</v>
       </c>
       <c r="C99">
-        <v>-306.0079342145482</v>
+        <v>-316.3286851770196</v>
       </c>
       <c r="D99">
-        <v>256.0760657854518</v>
+        <v>254.4273148229804</v>
       </c>
       <c r="E99">
-        <v>304.9839999999999</v>
+        <v>313.6559999999999</v>
       </c>
       <c r="F99">
-        <v>841.184</v>
+        <v>849.856</v>
       </c>
       <c r="G99">
         <v>279.1</v>
@@ -9405,37 +9405,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M99">
-        <v>198.3511872</v>
+        <v>200.3960448</v>
       </c>
       <c r="N99">
-        <v>-117.9511872</v>
+        <v>-119.9960448</v>
       </c>
       <c r="O99">
-        <v>-29.4877968</v>
+        <v>-29.9990112</v>
       </c>
       <c r="P99">
-        <v>-88.46339039999999</v>
+        <v>-89.99703359999999</v>
       </c>
       <c r="Q99">
-        <v>-46.5633904</v>
+        <v>-48.0970336</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.575927236182034</v>
+        <v>2.340990854273051</v>
       </c>
       <c r="T99">
-        <v>29.82502785751486</v>
+        <v>44.73754178627228</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1013354156521025</v>
+        <v>0.1003013807985097</v>
       </c>
       <c r="W99">
-        <v>0.2119051089892342</v>
+        <v>0.2121489344077114</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4053416626084102</v>
+        <v>0.4012055231940387</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2547257728050182</v>
+        <v>0.2566257728050182</v>
       </c>
       <c r="C100">
-        <v>-316.3286851770196</v>
+        <v>-326.628340928168</v>
       </c>
       <c r="D100">
-        <v>254.4273148229804</v>
+        <v>252.799659071832</v>
       </c>
       <c r="E100">
-        <v>313.6559999999999</v>
+        <v>322.328</v>
       </c>
       <c r="F100">
-        <v>849.856</v>
+        <v>858.528</v>
       </c>
       <c r="G100">
         <v>279.1</v>
@@ -9487,37 +9487,37 @@
         <v>80.40000000000001</v>
       </c>
       <c r="M100">
-        <v>200.3960448</v>
+        <v>202.4409024</v>
       </c>
       <c r="N100">
-        <v>-119.9960448</v>
+        <v>-122.0409024</v>
       </c>
       <c r="O100">
-        <v>-29.9990112</v>
+        <v>-30.5102256</v>
       </c>
       <c r="P100">
-        <v>-89.99703359999999</v>
+        <v>-91.53067679999999</v>
       </c>
       <c r="Q100">
-        <v>-48.0970336</v>
+        <v>-49.6306768</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.340990854273051</v>
+        <v>4.636181708546102</v>
       </c>
       <c r="T100">
-        <v>44.73754178627228</v>
+        <v>89.47508357254458</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1003013807985097</v>
+        <v>0.09928823553791866</v>
       </c>
       <c r="W100">
-        <v>0.2121489344077114</v>
+        <v>0.2123878340601588</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4012055231940387</v>
+        <v>0.3971529421516746</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2566257728050182</v>
-      </c>
-      <c r="C101">
-        <v>-326.628340928168</v>
-      </c>
-      <c r="D101">
-        <v>252.799659071832</v>
-      </c>
-      <c r="E101">
-        <v>322.328</v>
-      </c>
-      <c r="F101">
-        <v>858.528</v>
-      </c>
-      <c r="G101">
-        <v>279.1</v>
-      </c>
-      <c r="H101">
-        <v>331</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>122.3</v>
-      </c>
-      <c r="K101">
-        <v>41.9</v>
-      </c>
-      <c r="L101">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="M101">
-        <v>202.4409024</v>
-      </c>
-      <c r="N101">
-        <v>-122.0409024</v>
-      </c>
-      <c r="O101">
-        <v>-30.5102256</v>
-      </c>
-      <c r="P101">
-        <v>-91.53067679999999</v>
-      </c>
-      <c r="Q101">
-        <v>-49.6306768</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.636181708546102</v>
-      </c>
-      <c r="T101">
-        <v>89.47508357254458</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09928823553791866</v>
-      </c>
-      <c r="W101">
-        <v>0.2123878340601588</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3971529421516746</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
